--- a/Arquivos/nao_atualizaveis/Ativo_Prospecção IEL/Discagem_Ativo_Prospecção_IEL.xlsx
+++ b/Arquivos/nao_atualizaveis/Ativo_Prospecção IEL/Discagem_Ativo_Prospecção_IEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Ativo_Prospecção IEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377FB8DD-B066-4A94-B804-72B7F4C3FFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD48DDFC-F0C6-4642-AEB4-C546785828E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8576016-ED65-4244-9F24-F723354B3EF0}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8253" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9110" uniqueCount="223">
   <si>
     <t>DATA</t>
   </si>
@@ -1536,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D24DB4E9-414F-485A-A3F2-E34A8848786F}">
-  <dimension ref="A1:S943"/>
+  <dimension ref="A1:S1050"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -47964,6 +47964,4632 @@
         <v>1.4120370370370369E-3</v>
       </c>
     </row>
+    <row r="944" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A944" s="1">
+        <v>46224.59134259259</v>
+      </c>
+      <c r="B944" t="s">
+        <v>19</v>
+      </c>
+      <c r="C944" t="s">
+        <v>20</v>
+      </c>
+      <c r="E944"/>
+      <c r="F944">
+        <v>2757826516</v>
+      </c>
+      <c r="G944" s="2">
+        <v>1784653892563380</v>
+      </c>
+      <c r="H944" t="s">
+        <v>195</v>
+      </c>
+      <c r="I944" t="s">
+        <v>145</v>
+      </c>
+      <c r="J944" t="s">
+        <v>197</v>
+      </c>
+      <c r="K944" t="s">
+        <v>21</v>
+      </c>
+      <c r="N944" t="s">
+        <v>24</v>
+      </c>
+      <c r="O944">
+        <v>19</v>
+      </c>
+      <c r="R944" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="S944" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="945" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A945" s="1">
+        <v>46224.591597222221</v>
+      </c>
+      <c r="B945" t="s">
+        <v>19</v>
+      </c>
+      <c r="C945" t="s">
+        <v>20</v>
+      </c>
+      <c r="E945"/>
+      <c r="F945">
+        <v>2757826538</v>
+      </c>
+      <c r="G945" s="2">
+        <v>1784653914563960</v>
+      </c>
+      <c r="H945" t="s">
+        <v>195</v>
+      </c>
+      <c r="I945" t="s">
+        <v>145</v>
+      </c>
+      <c r="J945" t="s">
+        <v>197</v>
+      </c>
+      <c r="K945" t="s">
+        <v>21</v>
+      </c>
+      <c r="N945" t="s">
+        <v>24</v>
+      </c>
+      <c r="O945">
+        <v>19</v>
+      </c>
+      <c r="R945" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="S945" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="946" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A946" s="1">
+        <v>46224.592002314814</v>
+      </c>
+      <c r="B946" t="s">
+        <v>19</v>
+      </c>
+      <c r="C946" t="s">
+        <v>20</v>
+      </c>
+      <c r="E946"/>
+      <c r="F946">
+        <v>2784653969</v>
+      </c>
+      <c r="G946" s="2">
+        <v>1784653949565020</v>
+      </c>
+      <c r="H946" t="s">
+        <v>195</v>
+      </c>
+      <c r="I946" t="s">
+        <v>113</v>
+      </c>
+      <c r="J946" t="s">
+        <v>197</v>
+      </c>
+      <c r="K946" t="s">
+        <v>21</v>
+      </c>
+      <c r="N946" t="s">
+        <v>24</v>
+      </c>
+      <c r="O946">
+        <v>19</v>
+      </c>
+      <c r="R946" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="S946" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="947" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A947" s="1">
+        <v>46224.592372685183</v>
+      </c>
+      <c r="B947" t="s">
+        <v>19</v>
+      </c>
+      <c r="C947" t="s">
+        <v>20</v>
+      </c>
+      <c r="E947"/>
+      <c r="F947">
+        <v>2753088898</v>
+      </c>
+      <c r="G947" s="2">
+        <v>1784653981566240</v>
+      </c>
+      <c r="H947" t="s">
+        <v>195</v>
+      </c>
+      <c r="I947" t="s">
+        <v>146</v>
+      </c>
+      <c r="J947" t="s">
+        <v>197</v>
+      </c>
+      <c r="K947" t="s">
+        <v>21</v>
+      </c>
+      <c r="N947" t="s">
+        <v>24</v>
+      </c>
+      <c r="O947">
+        <v>19</v>
+      </c>
+      <c r="R947" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S947" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="948" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A948" s="1">
+        <v>46224.592627314814</v>
+      </c>
+      <c r="B948" t="s">
+        <v>19</v>
+      </c>
+      <c r="C948" t="s">
+        <v>20</v>
+      </c>
+      <c r="E948"/>
+      <c r="F948">
+        <v>2753088920</v>
+      </c>
+      <c r="G948" s="2">
+        <v>1784654003566850</v>
+      </c>
+      <c r="H948" t="s">
+        <v>195</v>
+      </c>
+      <c r="I948" t="s">
+        <v>146</v>
+      </c>
+      <c r="J948" t="s">
+        <v>197</v>
+      </c>
+      <c r="K948" t="s">
+        <v>25</v>
+      </c>
+      <c r="L948" t="s">
+        <v>26</v>
+      </c>
+      <c r="N948" t="s">
+        <v>22</v>
+      </c>
+      <c r="O948">
+        <v>16</v>
+      </c>
+      <c r="R948" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="S948" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="949" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A949" s="1">
+        <v>46224.59306712963</v>
+      </c>
+      <c r="B949" t="s">
+        <v>19</v>
+      </c>
+      <c r="C949" t="s">
+        <v>20</v>
+      </c>
+      <c r="E949"/>
+      <c r="F949">
+        <v>2753088958</v>
+      </c>
+      <c r="G949" s="2">
+        <v>1784654041567740</v>
+      </c>
+      <c r="H949" t="s">
+        <v>195</v>
+      </c>
+      <c r="I949" t="s">
+        <v>146</v>
+      </c>
+      <c r="J949" t="s">
+        <v>197</v>
+      </c>
+      <c r="K949" t="s">
+        <v>21</v>
+      </c>
+      <c r="N949" t="s">
+        <v>24</v>
+      </c>
+      <c r="O949">
+        <v>19</v>
+      </c>
+      <c r="R949" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="S949" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="950" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A950" s="1">
+        <v>46224.593993055554</v>
+      </c>
+      <c r="B950" t="s">
+        <v>19</v>
+      </c>
+      <c r="C950" t="s">
+        <v>20</v>
+      </c>
+      <c r="E950"/>
+      <c r="F950">
+        <v>2782574735</v>
+      </c>
+      <c r="G950" s="2">
+        <v>1784654121569070</v>
+      </c>
+      <c r="H950" t="s">
+        <v>195</v>
+      </c>
+      <c r="I950" t="s">
+        <v>147</v>
+      </c>
+      <c r="J950" t="s">
+        <v>197</v>
+      </c>
+      <c r="K950" t="s">
+        <v>25</v>
+      </c>
+      <c r="L950" t="s">
+        <v>26</v>
+      </c>
+      <c r="N950" t="s">
+        <v>22</v>
+      </c>
+      <c r="O950">
+        <v>16</v>
+      </c>
+      <c r="R950" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S950" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+    </row>
+    <row r="951" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A951" s="1">
+        <v>46224.595324074071</v>
+      </c>
+      <c r="B951" t="s">
+        <v>19</v>
+      </c>
+      <c r="C951" t="s">
+        <v>20</v>
+      </c>
+      <c r="E951"/>
+      <c r="F951">
+        <v>2782574849</v>
+      </c>
+      <c r="G951" s="2">
+        <v>1784654236572760</v>
+      </c>
+      <c r="H951" t="s">
+        <v>195</v>
+      </c>
+      <c r="I951" t="s">
+        <v>147</v>
+      </c>
+      <c r="J951" t="s">
+        <v>197</v>
+      </c>
+      <c r="K951" t="s">
+        <v>25</v>
+      </c>
+      <c r="L951" t="s">
+        <v>26</v>
+      </c>
+      <c r="N951" t="s">
+        <v>24</v>
+      </c>
+      <c r="O951">
+        <v>16</v>
+      </c>
+      <c r="R951" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S951" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="952" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A952" s="1">
+        <v>46224.596041666664</v>
+      </c>
+      <c r="B952" t="s">
+        <v>19</v>
+      </c>
+      <c r="C952" t="s">
+        <v>20</v>
+      </c>
+      <c r="E952"/>
+      <c r="F952">
+        <v>2773233174</v>
+      </c>
+      <c r="G952" s="2">
+        <v>1784654298574290</v>
+      </c>
+      <c r="H952" t="s">
+        <v>195</v>
+      </c>
+      <c r="I952" t="s">
+        <v>148</v>
+      </c>
+      <c r="J952" t="s">
+        <v>197</v>
+      </c>
+      <c r="K952" t="s">
+        <v>21</v>
+      </c>
+      <c r="N952" t="s">
+        <v>24</v>
+      </c>
+      <c r="O952">
+        <v>19</v>
+      </c>
+      <c r="R952" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S952" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="953" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A953" s="1">
+        <v>46224.596597222226</v>
+      </c>
+      <c r="B953" t="s">
+        <v>19</v>
+      </c>
+      <c r="C953" t="s">
+        <v>20</v>
+      </c>
+      <c r="E953"/>
+      <c r="F953">
+        <v>2773233222</v>
+      </c>
+      <c r="G953" s="2">
+        <v>1784654346575860</v>
+      </c>
+      <c r="H953" t="s">
+        <v>195</v>
+      </c>
+      <c r="I953" t="s">
+        <v>148</v>
+      </c>
+      <c r="J953" t="s">
+        <v>197</v>
+      </c>
+      <c r="K953" t="s">
+        <v>25</v>
+      </c>
+      <c r="L953" t="s">
+        <v>28</v>
+      </c>
+      <c r="N953" t="s">
+        <v>24</v>
+      </c>
+      <c r="O953">
+        <v>16</v>
+      </c>
+      <c r="R953" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="S953" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="954" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A954" s="1">
+        <v>46224.597638888888</v>
+      </c>
+      <c r="B954" t="s">
+        <v>19</v>
+      </c>
+      <c r="C954" t="s">
+        <v>20</v>
+      </c>
+      <c r="E954"/>
+      <c r="F954">
+        <v>2783187882</v>
+      </c>
+      <c r="G954" s="2">
+        <v>1784654436578130</v>
+      </c>
+      <c r="H954" t="s">
+        <v>195</v>
+      </c>
+      <c r="I954" t="s">
+        <v>149</v>
+      </c>
+      <c r="J954" t="s">
+        <v>197</v>
+      </c>
+      <c r="K954" t="s">
+        <v>21</v>
+      </c>
+      <c r="N954" t="s">
+        <v>24</v>
+      </c>
+      <c r="O954">
+        <v>19</v>
+      </c>
+      <c r="R954" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S954" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="955" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A955" s="1">
+        <v>46224.597824074073</v>
+      </c>
+      <c r="B955" t="s">
+        <v>19</v>
+      </c>
+      <c r="C955" t="s">
+        <v>20</v>
+      </c>
+      <c r="E955"/>
+      <c r="F955">
+        <v>2783187898</v>
+      </c>
+      <c r="G955" s="2">
+        <v>1784654452578590</v>
+      </c>
+      <c r="H955" t="s">
+        <v>195</v>
+      </c>
+      <c r="I955" t="s">
+        <v>149</v>
+      </c>
+      <c r="J955" t="s">
+        <v>197</v>
+      </c>
+      <c r="K955" t="s">
+        <v>25</v>
+      </c>
+      <c r="L955" t="s">
+        <v>28</v>
+      </c>
+      <c r="N955" t="s">
+        <v>24</v>
+      </c>
+      <c r="O955">
+        <v>16</v>
+      </c>
+      <c r="R955" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="S955" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="956" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A956" s="1">
+        <v>46224.598530092589</v>
+      </c>
+      <c r="B956" t="s">
+        <v>19</v>
+      </c>
+      <c r="C956" t="s">
+        <v>20</v>
+      </c>
+      <c r="E956"/>
+      <c r="F956">
+        <v>2783187959</v>
+      </c>
+      <c r="G956" s="2">
+        <v>1784654513580150</v>
+      </c>
+      <c r="H956" t="s">
+        <v>195</v>
+      </c>
+      <c r="I956" t="s">
+        <v>149</v>
+      </c>
+      <c r="J956" t="s">
+        <v>197</v>
+      </c>
+      <c r="K956" t="s">
+        <v>21</v>
+      </c>
+      <c r="N956" t="s">
+        <v>24</v>
+      </c>
+      <c r="O956">
+        <v>19</v>
+      </c>
+      <c r="R956" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="S956" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="957" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A957" s="1">
+        <v>46224.59920138889</v>
+      </c>
+      <c r="B957" t="s">
+        <v>19</v>
+      </c>
+      <c r="C957" t="s">
+        <v>20</v>
+      </c>
+      <c r="E957"/>
+      <c r="F957">
+        <v>2768702076</v>
+      </c>
+      <c r="G957" s="2">
+        <v>1784654571582520</v>
+      </c>
+      <c r="H957" t="s">
+        <v>195</v>
+      </c>
+      <c r="I957" t="s">
+        <v>150</v>
+      </c>
+      <c r="J957" t="s">
+        <v>197</v>
+      </c>
+      <c r="K957" t="s">
+        <v>25</v>
+      </c>
+      <c r="L957" t="s">
+        <v>26</v>
+      </c>
+      <c r="N957" t="s">
+        <v>24</v>
+      </c>
+      <c r="O957">
+        <v>16</v>
+      </c>
+      <c r="R957" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="S957" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+    </row>
+    <row r="958" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A958" s="1">
+        <v>46224.599710648145</v>
+      </c>
+      <c r="B958" t="s">
+        <v>19</v>
+      </c>
+      <c r="C958" t="s">
+        <v>20</v>
+      </c>
+      <c r="E958"/>
+      <c r="F958">
+        <v>2768702120</v>
+      </c>
+      <c r="G958" s="2">
+        <v>1784654615584030</v>
+      </c>
+      <c r="H958" t="s">
+        <v>195</v>
+      </c>
+      <c r="I958" t="s">
+        <v>150</v>
+      </c>
+      <c r="J958" t="s">
+        <v>197</v>
+      </c>
+      <c r="K958" t="s">
+        <v>21</v>
+      </c>
+      <c r="N958" t="s">
+        <v>24</v>
+      </c>
+      <c r="O958">
+        <v>19</v>
+      </c>
+      <c r="R958" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+      <c r="S958" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="959" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A959" s="1">
+        <v>46224.6</v>
+      </c>
+      <c r="B959" t="s">
+        <v>19</v>
+      </c>
+      <c r="C959" t="s">
+        <v>20</v>
+      </c>
+      <c r="E959"/>
+      <c r="F959">
+        <v>2768702145</v>
+      </c>
+      <c r="G959" s="2">
+        <v>1784654640584660</v>
+      </c>
+      <c r="H959" t="s">
+        <v>195</v>
+      </c>
+      <c r="I959" t="s">
+        <v>150</v>
+      </c>
+      <c r="J959" t="s">
+        <v>197</v>
+      </c>
+      <c r="K959" t="s">
+        <v>25</v>
+      </c>
+      <c r="L959" t="s">
+        <v>132</v>
+      </c>
+      <c r="N959" t="s">
+        <v>22</v>
+      </c>
+      <c r="O959">
+        <v>16</v>
+      </c>
+      <c r="R959" s="3">
+        <v>9.7222222222222219E-4</v>
+      </c>
+      <c r="S959" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="960" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A960" s="1">
+        <v>46224.601261574076</v>
+      </c>
+      <c r="B960" t="s">
+        <v>19</v>
+      </c>
+      <c r="C960" t="s">
+        <v>20</v>
+      </c>
+      <c r="E960"/>
+      <c r="F960">
+        <v>2768702254</v>
+      </c>
+      <c r="G960" s="2">
+        <v>1784654749587940</v>
+      </c>
+      <c r="H960" t="s">
+        <v>195</v>
+      </c>
+      <c r="I960" t="s">
+        <v>150</v>
+      </c>
+      <c r="J960" t="s">
+        <v>197</v>
+      </c>
+      <c r="K960" t="s">
+        <v>21</v>
+      </c>
+      <c r="N960" t="s">
+        <v>24</v>
+      </c>
+      <c r="O960">
+        <v>19</v>
+      </c>
+      <c r="R960" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="S960" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="961" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A961" s="1">
+        <v>46224.602187500001</v>
+      </c>
+      <c r="B961" t="s">
+        <v>19</v>
+      </c>
+      <c r="C961" t="s">
+        <v>20</v>
+      </c>
+      <c r="E961"/>
+      <c r="F961">
+        <v>2784512557</v>
+      </c>
+      <c r="G961" s="2">
+        <v>1784654829590450</v>
+      </c>
+      <c r="H961" t="s">
+        <v>195</v>
+      </c>
+      <c r="I961" t="s">
+        <v>151</v>
+      </c>
+      <c r="J961" t="s">
+        <v>197</v>
+      </c>
+      <c r="K961" t="s">
+        <v>25</v>
+      </c>
+      <c r="L961" t="s">
+        <v>26</v>
+      </c>
+      <c r="N961" t="s">
+        <v>24</v>
+      </c>
+      <c r="O961">
+        <v>16</v>
+      </c>
+      <c r="R961" s="3">
+        <v>8.3333333333333339E-4</v>
+      </c>
+      <c r="S961" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="962" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A962" s="1">
+        <v>46224.603344907409</v>
+      </c>
+      <c r="B962" t="s">
+        <v>19</v>
+      </c>
+      <c r="C962" t="s">
+        <v>20</v>
+      </c>
+      <c r="E962"/>
+      <c r="F962">
+        <v>2760676997</v>
+      </c>
+      <c r="G962" s="2">
+        <v>1784654929592750</v>
+      </c>
+      <c r="H962" t="s">
+        <v>195</v>
+      </c>
+      <c r="I962" t="s">
+        <v>152</v>
+      </c>
+      <c r="J962" t="s">
+        <v>197</v>
+      </c>
+      <c r="K962" t="s">
+        <v>25</v>
+      </c>
+      <c r="L962" t="s">
+        <v>28</v>
+      </c>
+      <c r="N962" t="s">
+        <v>24</v>
+      </c>
+      <c r="O962">
+        <v>16</v>
+      </c>
+      <c r="R962" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S962" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="963" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A963" s="1">
+        <v>46224.603541666664</v>
+      </c>
+      <c r="B963" t="s">
+        <v>19</v>
+      </c>
+      <c r="C963" t="s">
+        <v>20</v>
+      </c>
+      <c r="E963"/>
+      <c r="F963">
+        <v>2760677014</v>
+      </c>
+      <c r="G963" s="2">
+        <v>1784654946593310</v>
+      </c>
+      <c r="H963" t="s">
+        <v>195</v>
+      </c>
+      <c r="I963" t="s">
+        <v>152</v>
+      </c>
+      <c r="J963" t="s">
+        <v>197</v>
+      </c>
+      <c r="K963" t="s">
+        <v>21</v>
+      </c>
+      <c r="N963" t="s">
+        <v>24</v>
+      </c>
+      <c r="O963">
+        <v>19</v>
+      </c>
+      <c r="R963" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="S963" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="964" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A964" s="1">
+        <v>46224.604328703703</v>
+      </c>
+      <c r="B964" t="s">
+        <v>19</v>
+      </c>
+      <c r="C964" t="s">
+        <v>20</v>
+      </c>
+      <c r="E964"/>
+      <c r="F964">
+        <v>2749317456</v>
+      </c>
+      <c r="G964" s="2">
+        <v>1784655014595150</v>
+      </c>
+      <c r="H964" t="s">
+        <v>195</v>
+      </c>
+      <c r="I964" t="s">
+        <v>153</v>
+      </c>
+      <c r="J964" t="s">
+        <v>197</v>
+      </c>
+      <c r="K964" t="s">
+        <v>25</v>
+      </c>
+      <c r="L964" t="s">
+        <v>26</v>
+      </c>
+      <c r="N964" t="s">
+        <v>24</v>
+      </c>
+      <c r="O964">
+        <v>16</v>
+      </c>
+      <c r="R964" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="S964" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="965" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A965" s="1">
+        <v>46224.604722222219</v>
+      </c>
+      <c r="B965" t="s">
+        <v>19</v>
+      </c>
+      <c r="C965" t="s">
+        <v>20</v>
+      </c>
+      <c r="E965"/>
+      <c r="F965">
+        <v>2749317490</v>
+      </c>
+      <c r="G965" s="2">
+        <v>1784655048596370</v>
+      </c>
+      <c r="H965" t="s">
+        <v>195</v>
+      </c>
+      <c r="I965" t="s">
+        <v>153</v>
+      </c>
+      <c r="J965" t="s">
+        <v>197</v>
+      </c>
+      <c r="K965" t="s">
+        <v>21</v>
+      </c>
+      <c r="N965" t="s">
+        <v>24</v>
+      </c>
+      <c r="O965">
+        <v>19</v>
+      </c>
+      <c r="R965" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S965" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="966" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A966" s="1">
+        <v>46224.605439814812</v>
+      </c>
+      <c r="B966" t="s">
+        <v>19</v>
+      </c>
+      <c r="C966" t="s">
+        <v>20</v>
+      </c>
+      <c r="E966"/>
+      <c r="F966">
+        <v>2753881853</v>
+      </c>
+      <c r="G966" s="2">
+        <v>1784655110598480</v>
+      </c>
+      <c r="H966" t="s">
+        <v>195</v>
+      </c>
+      <c r="I966" t="s">
+        <v>154</v>
+      </c>
+      <c r="J966" t="s">
+        <v>197</v>
+      </c>
+      <c r="K966" t="s">
+        <v>21</v>
+      </c>
+      <c r="N966" t="s">
+        <v>24</v>
+      </c>
+      <c r="O966">
+        <v>19</v>
+      </c>
+      <c r="R966" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S966" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="967" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A967" s="1">
+        <v>46224.60560185185</v>
+      </c>
+      <c r="B967" t="s">
+        <v>19</v>
+      </c>
+      <c r="C967" t="s">
+        <v>20</v>
+      </c>
+      <c r="E967"/>
+      <c r="F967">
+        <v>2753881867</v>
+      </c>
+      <c r="G967" s="2">
+        <v>1784655124598880</v>
+      </c>
+      <c r="H967" t="s">
+        <v>195</v>
+      </c>
+      <c r="I967" t="s">
+        <v>154</v>
+      </c>
+      <c r="J967" t="s">
+        <v>197</v>
+      </c>
+      <c r="K967" t="s">
+        <v>21</v>
+      </c>
+      <c r="N967" t="s">
+        <v>24</v>
+      </c>
+      <c r="O967">
+        <v>19</v>
+      </c>
+      <c r="R967" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S967" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="968" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A968" s="1">
+        <v>46224.605763888889</v>
+      </c>
+      <c r="B968" t="s">
+        <v>19</v>
+      </c>
+      <c r="C968" t="s">
+        <v>20</v>
+      </c>
+      <c r="E968"/>
+      <c r="F968">
+        <v>2753881881</v>
+      </c>
+      <c r="G968" s="2">
+        <v>1784655138599100</v>
+      </c>
+      <c r="H968" t="s">
+        <v>195</v>
+      </c>
+      <c r="I968" t="s">
+        <v>154</v>
+      </c>
+      <c r="J968" t="s">
+        <v>197</v>
+      </c>
+      <c r="K968" t="s">
+        <v>21</v>
+      </c>
+      <c r="N968" t="s">
+        <v>24</v>
+      </c>
+      <c r="O968">
+        <v>19</v>
+      </c>
+      <c r="R968" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S968" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="969" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A969" s="1">
+        <v>46224.606157407405</v>
+      </c>
+      <c r="B969" t="s">
+        <v>19</v>
+      </c>
+      <c r="C969" t="s">
+        <v>20</v>
+      </c>
+      <c r="E969"/>
+      <c r="F969">
+        <v>2772665392</v>
+      </c>
+      <c r="G969" s="2">
+        <v>1784655172600350</v>
+      </c>
+      <c r="H969" t="s">
+        <v>195</v>
+      </c>
+      <c r="I969" t="s">
+        <v>155</v>
+      </c>
+      <c r="J969" t="s">
+        <v>197</v>
+      </c>
+      <c r="K969" t="s">
+        <v>21</v>
+      </c>
+      <c r="N969" t="s">
+        <v>24</v>
+      </c>
+      <c r="O969">
+        <v>19</v>
+      </c>
+      <c r="R969" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="S969" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="970" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A970" s="1">
+        <v>46224.606423611112</v>
+      </c>
+      <c r="B970" t="s">
+        <v>19</v>
+      </c>
+      <c r="C970" t="s">
+        <v>20</v>
+      </c>
+      <c r="E970"/>
+      <c r="F970">
+        <v>2772665415</v>
+      </c>
+      <c r="G970" s="2">
+        <v>1784655195601080</v>
+      </c>
+      <c r="H970" t="s">
+        <v>195</v>
+      </c>
+      <c r="I970" t="s">
+        <v>155</v>
+      </c>
+      <c r="J970" t="s">
+        <v>197</v>
+      </c>
+      <c r="K970" t="s">
+        <v>21</v>
+      </c>
+      <c r="N970" t="s">
+        <v>24</v>
+      </c>
+      <c r="O970">
+        <v>19</v>
+      </c>
+      <c r="R970" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="S970" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="971" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A971" s="1">
+        <v>46224.60732638889</v>
+      </c>
+      <c r="B971" t="s">
+        <v>19</v>
+      </c>
+      <c r="C971" t="s">
+        <v>20</v>
+      </c>
+      <c r="E971"/>
+      <c r="F971">
+        <v>2772905010</v>
+      </c>
+      <c r="G971" s="2">
+        <v>1784655273603460</v>
+      </c>
+      <c r="H971" t="s">
+        <v>195</v>
+      </c>
+      <c r="I971" t="s">
+        <v>156</v>
+      </c>
+      <c r="J971" t="s">
+        <v>197</v>
+      </c>
+      <c r="K971" t="s">
+        <v>21</v>
+      </c>
+      <c r="N971" t="s">
+        <v>24</v>
+      </c>
+      <c r="O971">
+        <v>19</v>
+      </c>
+      <c r="R971" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S971" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="972" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A972" s="1">
+        <v>46224.607488425929</v>
+      </c>
+      <c r="B972" t="s">
+        <v>19</v>
+      </c>
+      <c r="C972" t="s">
+        <v>20</v>
+      </c>
+      <c r="E972"/>
+      <c r="F972">
+        <v>2772905024</v>
+      </c>
+      <c r="G972" s="2">
+        <v>1784655287603770</v>
+      </c>
+      <c r="H972" t="s">
+        <v>195</v>
+      </c>
+      <c r="I972" t="s">
+        <v>156</v>
+      </c>
+      <c r="J972" t="s">
+        <v>197</v>
+      </c>
+      <c r="K972" t="s">
+        <v>25</v>
+      </c>
+      <c r="L972" t="s">
+        <v>65</v>
+      </c>
+      <c r="N972" t="s">
+        <v>22</v>
+      </c>
+      <c r="O972">
+        <v>16</v>
+      </c>
+      <c r="R972" s="3">
+        <v>1.5972222222222223E-3</v>
+      </c>
+      <c r="S972" s="3">
+        <v>1.2268518518518518E-3</v>
+      </c>
+    </row>
+    <row r="973" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A973" s="1">
+        <v>46224.611122685186</v>
+      </c>
+      <c r="B973" t="s">
+        <v>19</v>
+      </c>
+      <c r="C973" t="s">
+        <v>20</v>
+      </c>
+      <c r="E973"/>
+      <c r="F973">
+        <v>2784400512</v>
+      </c>
+      <c r="G973" s="2">
+        <v>1784655601614410</v>
+      </c>
+      <c r="H973" t="s">
+        <v>195</v>
+      </c>
+      <c r="I973" t="s">
+        <v>157</v>
+      </c>
+      <c r="J973" t="s">
+        <v>197</v>
+      </c>
+      <c r="K973" t="s">
+        <v>25</v>
+      </c>
+      <c r="L973" t="s">
+        <v>39</v>
+      </c>
+      <c r="N973" t="s">
+        <v>22</v>
+      </c>
+      <c r="O973">
+        <v>16</v>
+      </c>
+      <c r="R973" s="3">
+        <v>1.3541666666666667E-3</v>
+      </c>
+      <c r="S973" s="3">
+        <v>1.2152777777777778E-3</v>
+      </c>
+    </row>
+    <row r="974" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A974" s="1">
+        <v>46224.613032407404</v>
+      </c>
+      <c r="B974" t="s">
+        <v>19</v>
+      </c>
+      <c r="C974" t="s">
+        <v>20</v>
+      </c>
+      <c r="E974"/>
+      <c r="F974">
+        <v>2778926805</v>
+      </c>
+      <c r="G974" s="2">
+        <v>1784655766619580</v>
+      </c>
+      <c r="H974" t="s">
+        <v>195</v>
+      </c>
+      <c r="I974" t="s">
+        <v>158</v>
+      </c>
+      <c r="J974" t="s">
+        <v>197</v>
+      </c>
+      <c r="K974" t="s">
+        <v>21</v>
+      </c>
+      <c r="N974" t="s">
+        <v>24</v>
+      </c>
+      <c r="O974">
+        <v>19</v>
+      </c>
+      <c r="R974" s="3">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="S974" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="975" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A975" s="1">
+        <v>46224.613321759258</v>
+      </c>
+      <c r="B975" t="s">
+        <v>19</v>
+      </c>
+      <c r="C975" t="s">
+        <v>20</v>
+      </c>
+      <c r="E975"/>
+      <c r="F975">
+        <v>2778926830</v>
+      </c>
+      <c r="G975" s="2">
+        <v>1784655791620300</v>
+      </c>
+      <c r="H975" t="s">
+        <v>195</v>
+      </c>
+      <c r="I975" t="s">
+        <v>158</v>
+      </c>
+      <c r="J975" t="s">
+        <v>197</v>
+      </c>
+      <c r="K975" t="s">
+        <v>21</v>
+      </c>
+      <c r="N975" t="s">
+        <v>24</v>
+      </c>
+      <c r="O975">
+        <v>19</v>
+      </c>
+      <c r="R975" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="S975" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="976" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A976" s="1">
+        <v>46224.613969907405</v>
+      </c>
+      <c r="B976" t="s">
+        <v>19</v>
+      </c>
+      <c r="C976" t="s">
+        <v>20</v>
+      </c>
+      <c r="E976"/>
+      <c r="F976">
+        <v>2772975154</v>
+      </c>
+      <c r="G976" s="2">
+        <v>1784655847621610</v>
+      </c>
+      <c r="H976" t="s">
+        <v>195</v>
+      </c>
+      <c r="I976" t="s">
+        <v>159</v>
+      </c>
+      <c r="J976" t="s">
+        <v>197</v>
+      </c>
+      <c r="K976" t="s">
+        <v>21</v>
+      </c>
+      <c r="N976" t="s">
+        <v>24</v>
+      </c>
+      <c r="O976">
+        <v>19</v>
+      </c>
+      <c r="R976" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S976" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="977" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A977" s="1">
+        <v>46224.614120370374</v>
+      </c>
+      <c r="B977" t="s">
+        <v>19</v>
+      </c>
+      <c r="C977" t="s">
+        <v>20</v>
+      </c>
+      <c r="E977"/>
+      <c r="F977">
+        <v>2772975167</v>
+      </c>
+      <c r="G977" s="2">
+        <v>1784655860622090</v>
+      </c>
+      <c r="H977" t="s">
+        <v>195</v>
+      </c>
+      <c r="I977" t="s">
+        <v>159</v>
+      </c>
+      <c r="J977" t="s">
+        <v>197</v>
+      </c>
+      <c r="K977" t="s">
+        <v>21</v>
+      </c>
+      <c r="N977" t="s">
+        <v>24</v>
+      </c>
+      <c r="O977">
+        <v>19</v>
+      </c>
+      <c r="R977" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S977" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="978" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A978" s="1">
+        <v>46224.614236111112</v>
+      </c>
+      <c r="B978" t="s">
+        <v>19</v>
+      </c>
+      <c r="C978" t="s">
+        <v>20</v>
+      </c>
+      <c r="E978"/>
+      <c r="F978">
+        <v>2772975177</v>
+      </c>
+      <c r="G978" s="2">
+        <v>1784655870622290</v>
+      </c>
+      <c r="H978" t="s">
+        <v>195</v>
+      </c>
+      <c r="I978" t="s">
+        <v>159</v>
+      </c>
+      <c r="J978" t="s">
+        <v>197</v>
+      </c>
+      <c r="K978" t="s">
+        <v>21</v>
+      </c>
+      <c r="N978" t="s">
+        <v>24</v>
+      </c>
+      <c r="O978">
+        <v>19</v>
+      </c>
+      <c r="R978" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S978" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="979" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A979" s="1">
+        <v>46224.615127314813</v>
+      </c>
+      <c r="B979" t="s">
+        <v>19</v>
+      </c>
+      <c r="C979" t="s">
+        <v>20</v>
+      </c>
+      <c r="E979"/>
+      <c r="F979">
+        <v>2779854391</v>
+      </c>
+      <c r="G979" s="2">
+        <v>1784655947624480</v>
+      </c>
+      <c r="H979" t="s">
+        <v>195</v>
+      </c>
+      <c r="I979" t="s">
+        <v>160</v>
+      </c>
+      <c r="J979" t="s">
+        <v>197</v>
+      </c>
+      <c r="K979" t="s">
+        <v>25</v>
+      </c>
+      <c r="L979" t="s">
+        <v>28</v>
+      </c>
+      <c r="N979" t="s">
+        <v>24</v>
+      </c>
+      <c r="O979">
+        <v>16</v>
+      </c>
+      <c r="R979" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S979" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="980" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A980" s="1">
+        <v>46224.615324074075</v>
+      </c>
+      <c r="B980" t="s">
+        <v>19</v>
+      </c>
+      <c r="C980" t="s">
+        <v>20</v>
+      </c>
+      <c r="E980"/>
+      <c r="F980">
+        <v>2779854408</v>
+      </c>
+      <c r="G980" s="2">
+        <v>1784655964625110</v>
+      </c>
+      <c r="H980" t="s">
+        <v>195</v>
+      </c>
+      <c r="I980" t="s">
+        <v>160</v>
+      </c>
+      <c r="J980" t="s">
+        <v>197</v>
+      </c>
+      <c r="K980" t="s">
+        <v>25</v>
+      </c>
+      <c r="L980" t="s">
+        <v>28</v>
+      </c>
+      <c r="N980" t="s">
+        <v>24</v>
+      </c>
+      <c r="O980">
+        <v>16</v>
+      </c>
+      <c r="R980" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S980" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="981" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A981" s="1">
+        <v>46224.615787037037</v>
+      </c>
+      <c r="B981" t="s">
+        <v>19</v>
+      </c>
+      <c r="C981" t="s">
+        <v>20</v>
+      </c>
+      <c r="E981"/>
+      <c r="F981">
+        <v>2767716421</v>
+      </c>
+      <c r="G981" s="2">
+        <v>1784656004625970</v>
+      </c>
+      <c r="H981" t="s">
+        <v>195</v>
+      </c>
+      <c r="I981" t="s">
+        <v>162</v>
+      </c>
+      <c r="J981" t="s">
+        <v>197</v>
+      </c>
+      <c r="K981" t="s">
+        <v>25</v>
+      </c>
+      <c r="L981" t="s">
+        <v>28</v>
+      </c>
+      <c r="N981" t="s">
+        <v>24</v>
+      </c>
+      <c r="O981">
+        <v>16</v>
+      </c>
+      <c r="R981" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S981" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="982" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A982" s="1">
+        <v>46224.616215277776</v>
+      </c>
+      <c r="B982" t="s">
+        <v>19</v>
+      </c>
+      <c r="C982" t="s">
+        <v>20</v>
+      </c>
+      <c r="E982"/>
+      <c r="F982">
+        <v>2767716458</v>
+      </c>
+      <c r="G982" s="2">
+        <v>1784656041626890</v>
+      </c>
+      <c r="H982" t="s">
+        <v>195</v>
+      </c>
+      <c r="I982" t="s">
+        <v>162</v>
+      </c>
+      <c r="J982" t="s">
+        <v>197</v>
+      </c>
+      <c r="K982" t="s">
+        <v>25</v>
+      </c>
+      <c r="L982" t="s">
+        <v>28</v>
+      </c>
+      <c r="N982" t="s">
+        <v>24</v>
+      </c>
+      <c r="O982">
+        <v>16</v>
+      </c>
+      <c r="R982" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S982" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="983" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A983" s="1">
+        <v>46224.616840277777</v>
+      </c>
+      <c r="B983" t="s">
+        <v>19</v>
+      </c>
+      <c r="C983" t="s">
+        <v>20</v>
+      </c>
+      <c r="E983"/>
+      <c r="F983">
+        <v>2769714228</v>
+      </c>
+      <c r="G983" s="2">
+        <v>1784656095628510</v>
+      </c>
+      <c r="H983" t="s">
+        <v>195</v>
+      </c>
+      <c r="I983" t="s">
+        <v>163</v>
+      </c>
+      <c r="J983" t="s">
+        <v>197</v>
+      </c>
+      <c r="K983" t="s">
+        <v>21</v>
+      </c>
+      <c r="N983" t="s">
+        <v>24</v>
+      </c>
+      <c r="O983">
+        <v>19</v>
+      </c>
+      <c r="R983" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S983" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="984" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A984" s="1">
+        <v>46224.616956018515</v>
+      </c>
+      <c r="B984" t="s">
+        <v>19</v>
+      </c>
+      <c r="C984" t="s">
+        <v>20</v>
+      </c>
+      <c r="E984"/>
+      <c r="F984">
+        <v>2769714238</v>
+      </c>
+      <c r="G984" s="2">
+        <v>1784656105628870</v>
+      </c>
+      <c r="H984" t="s">
+        <v>195</v>
+      </c>
+      <c r="I984" t="s">
+        <v>163</v>
+      </c>
+      <c r="J984" t="s">
+        <v>197</v>
+      </c>
+      <c r="K984" t="s">
+        <v>21</v>
+      </c>
+      <c r="N984" t="s">
+        <v>24</v>
+      </c>
+      <c r="O984">
+        <v>19</v>
+      </c>
+      <c r="R984" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="S984" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="985" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A985" s="1">
+        <v>46224.617407407408</v>
+      </c>
+      <c r="B985" t="s">
+        <v>19</v>
+      </c>
+      <c r="C985" t="s">
+        <v>20</v>
+      </c>
+      <c r="E985"/>
+      <c r="F985">
+        <v>2769714277</v>
+      </c>
+      <c r="G985" s="2">
+        <v>1784656144630300</v>
+      </c>
+      <c r="H985" t="s">
+        <v>195</v>
+      </c>
+      <c r="I985" t="s">
+        <v>163</v>
+      </c>
+      <c r="J985" t="s">
+        <v>197</v>
+      </c>
+      <c r="K985" t="s">
+        <v>21</v>
+      </c>
+      <c r="N985" t="s">
+        <v>24</v>
+      </c>
+      <c r="O985">
+        <v>19</v>
+      </c>
+      <c r="R985" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S985" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="986" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A986" s="1">
+        <v>46224.617743055554</v>
+      </c>
+      <c r="B986" t="s">
+        <v>19</v>
+      </c>
+      <c r="C986" t="s">
+        <v>20</v>
+      </c>
+      <c r="E986"/>
+      <c r="F986">
+        <v>2749154917</v>
+      </c>
+      <c r="G986" s="2">
+        <v>1784656173631070</v>
+      </c>
+      <c r="H986" t="s">
+        <v>195</v>
+      </c>
+      <c r="I986" t="s">
+        <v>164</v>
+      </c>
+      <c r="J986" t="s">
+        <v>197</v>
+      </c>
+      <c r="K986" t="s">
+        <v>25</v>
+      </c>
+      <c r="L986" t="s">
+        <v>28</v>
+      </c>
+      <c r="N986" t="s">
+        <v>24</v>
+      </c>
+      <c r="O986">
+        <v>16</v>
+      </c>
+      <c r="R986" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="S986" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+    </row>
+    <row r="987" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A987" s="1">
+        <v>46224.618611111109</v>
+      </c>
+      <c r="B987" t="s">
+        <v>19</v>
+      </c>
+      <c r="C987" t="s">
+        <v>20</v>
+      </c>
+      <c r="E987"/>
+      <c r="F987">
+        <v>2777276034</v>
+      </c>
+      <c r="G987" s="2">
+        <v>1784656248634240</v>
+      </c>
+      <c r="H987" t="s">
+        <v>195</v>
+      </c>
+      <c r="I987" t="s">
+        <v>165</v>
+      </c>
+      <c r="J987" t="s">
+        <v>197</v>
+      </c>
+      <c r="K987" t="s">
+        <v>25</v>
+      </c>
+      <c r="L987" t="s">
+        <v>26</v>
+      </c>
+      <c r="N987" t="s">
+        <v>24</v>
+      </c>
+      <c r="O987">
+        <v>16</v>
+      </c>
+      <c r="R987" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="S987" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="988" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A988" s="1">
+        <v>46224.619351851848</v>
+      </c>
+      <c r="B988" t="s">
+        <v>19</v>
+      </c>
+      <c r="C988" t="s">
+        <v>20</v>
+      </c>
+      <c r="E988"/>
+      <c r="F988">
+        <v>2777276098</v>
+      </c>
+      <c r="G988" s="2">
+        <v>1784656312637020</v>
+      </c>
+      <c r="H988" t="s">
+        <v>195</v>
+      </c>
+      <c r="I988" t="s">
+        <v>165</v>
+      </c>
+      <c r="J988" t="s">
+        <v>197</v>
+      </c>
+      <c r="K988" t="s">
+        <v>21</v>
+      </c>
+      <c r="N988" t="s">
+        <v>24</v>
+      </c>
+      <c r="O988">
+        <v>19</v>
+      </c>
+      <c r="R988" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S988" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="989" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A989" s="1">
+        <v>46224.620358796295</v>
+      </c>
+      <c r="B989" t="s">
+        <v>19</v>
+      </c>
+      <c r="C989" t="s">
+        <v>20</v>
+      </c>
+      <c r="E989"/>
+      <c r="F989">
+        <v>2781812174</v>
+      </c>
+      <c r="G989" s="2">
+        <v>1784656399640080</v>
+      </c>
+      <c r="H989" t="s">
+        <v>195</v>
+      </c>
+      <c r="I989" t="s">
+        <v>77</v>
+      </c>
+      <c r="J989" t="s">
+        <v>197</v>
+      </c>
+      <c r="K989" t="s">
+        <v>25</v>
+      </c>
+      <c r="L989" t="s">
+        <v>28</v>
+      </c>
+      <c r="N989" t="s">
+        <v>24</v>
+      </c>
+      <c r="O989">
+        <v>16</v>
+      </c>
+      <c r="R989" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="S989" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="990" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A990" s="1">
+        <v>46224.621076388888</v>
+      </c>
+      <c r="B990" t="s">
+        <v>19</v>
+      </c>
+      <c r="C990" t="s">
+        <v>20</v>
+      </c>
+      <c r="E990"/>
+      <c r="F990">
+        <v>2781812236</v>
+      </c>
+      <c r="G990" s="2">
+        <v>1784656461642190</v>
+      </c>
+      <c r="H990" t="s">
+        <v>195</v>
+      </c>
+      <c r="I990" t="s">
+        <v>77</v>
+      </c>
+      <c r="J990" t="s">
+        <v>197</v>
+      </c>
+      <c r="K990" t="s">
+        <v>25</v>
+      </c>
+      <c r="L990" t="s">
+        <v>28</v>
+      </c>
+      <c r="N990" t="s">
+        <v>24</v>
+      </c>
+      <c r="O990">
+        <v>16</v>
+      </c>
+      <c r="R990" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="S990" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="991" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A991" s="1">
+        <v>46224.623020833336</v>
+      </c>
+      <c r="B991" t="s">
+        <v>19</v>
+      </c>
+      <c r="C991" t="s">
+        <v>20</v>
+      </c>
+      <c r="E991"/>
+      <c r="F991">
+        <v>2781216580</v>
+      </c>
+      <c r="G991" s="2">
+        <v>1784656629649070</v>
+      </c>
+      <c r="H991" t="s">
+        <v>195</v>
+      </c>
+      <c r="I991" t="s">
+        <v>78</v>
+      </c>
+      <c r="J991" t="s">
+        <v>197</v>
+      </c>
+      <c r="K991" t="s">
+        <v>21</v>
+      </c>
+      <c r="N991" t="s">
+        <v>24</v>
+      </c>
+      <c r="O991">
+        <v>19</v>
+      </c>
+      <c r="R991" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="S991" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="992" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A992" s="1">
+        <v>46224.623240740744</v>
+      </c>
+      <c r="B992" t="s">
+        <v>19</v>
+      </c>
+      <c r="C992" t="s">
+        <v>20</v>
+      </c>
+      <c r="E992"/>
+      <c r="F992">
+        <v>2781216599</v>
+      </c>
+      <c r="G992" s="2">
+        <v>1784656648649790</v>
+      </c>
+      <c r="H992" t="s">
+        <v>195</v>
+      </c>
+      <c r="I992" t="s">
+        <v>78</v>
+      </c>
+      <c r="J992" t="s">
+        <v>197</v>
+      </c>
+      <c r="K992" t="s">
+        <v>21</v>
+      </c>
+      <c r="N992" t="s">
+        <v>24</v>
+      </c>
+      <c r="O992">
+        <v>19</v>
+      </c>
+      <c r="R992" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S992" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="993" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A993" s="1">
+        <v>46224.623668981483</v>
+      </c>
+      <c r="B993" t="s">
+        <v>19</v>
+      </c>
+      <c r="C993" t="s">
+        <v>20</v>
+      </c>
+      <c r="E993"/>
+      <c r="F993">
+        <v>1820310122</v>
+      </c>
+      <c r="G993" s="2">
+        <v>1784656685651450</v>
+      </c>
+      <c r="H993" t="s">
+        <v>195</v>
+      </c>
+      <c r="I993" t="s">
+        <v>79</v>
+      </c>
+      <c r="J993" t="s">
+        <v>197</v>
+      </c>
+      <c r="K993" t="s">
+        <v>21</v>
+      </c>
+      <c r="N993" t="s">
+        <v>22</v>
+      </c>
+      <c r="O993">
+        <v>1</v>
+      </c>
+      <c r="R993" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S993" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="994" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A994" s="1">
+        <v>46224.623877314814</v>
+      </c>
+      <c r="B994" t="s">
+        <v>19</v>
+      </c>
+      <c r="C994" t="s">
+        <v>20</v>
+      </c>
+      <c r="E994"/>
+      <c r="F994">
+        <v>1820310140</v>
+      </c>
+      <c r="G994" s="2">
+        <v>1784656703652240</v>
+      </c>
+      <c r="H994" t="s">
+        <v>195</v>
+      </c>
+      <c r="I994" t="s">
+        <v>79</v>
+      </c>
+      <c r="J994" t="s">
+        <v>197</v>
+      </c>
+      <c r="K994" t="s">
+        <v>21</v>
+      </c>
+      <c r="N994" t="s">
+        <v>22</v>
+      </c>
+      <c r="O994">
+        <v>1</v>
+      </c>
+      <c r="R994" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S994" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="995" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A995" s="1">
+        <v>46224.623981481483</v>
+      </c>
+      <c r="B995" t="s">
+        <v>19</v>
+      </c>
+      <c r="C995" t="s">
+        <v>20</v>
+      </c>
+      <c r="E995"/>
+      <c r="F995">
+        <v>1820310148</v>
+      </c>
+      <c r="G995" s="2">
+        <v>1784656711652580</v>
+      </c>
+      <c r="H995" t="s">
+        <v>195</v>
+      </c>
+      <c r="I995" t="s">
+        <v>79</v>
+      </c>
+      <c r="J995" t="s">
+        <v>197</v>
+      </c>
+      <c r="K995" t="s">
+        <v>21</v>
+      </c>
+      <c r="N995" t="s">
+        <v>22</v>
+      </c>
+      <c r="O995">
+        <v>1</v>
+      </c>
+      <c r="R995" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S995" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="996" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A996" s="1">
+        <v>46224.624097222222</v>
+      </c>
+      <c r="B996" t="s">
+        <v>19</v>
+      </c>
+      <c r="C996" t="s">
+        <v>20</v>
+      </c>
+      <c r="E996"/>
+      <c r="F996">
+        <v>1820310158</v>
+      </c>
+      <c r="G996" s="2">
+        <v>1784656721652960</v>
+      </c>
+      <c r="H996" t="s">
+        <v>195</v>
+      </c>
+      <c r="I996" t="s">
+        <v>79</v>
+      </c>
+      <c r="J996" t="s">
+        <v>197</v>
+      </c>
+      <c r="K996" t="s">
+        <v>21</v>
+      </c>
+      <c r="N996" t="s">
+        <v>22</v>
+      </c>
+      <c r="O996">
+        <v>1</v>
+      </c>
+      <c r="R996" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S996" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="997" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A997" s="1">
+        <v>46224.624479166669</v>
+      </c>
+      <c r="B997" t="s">
+        <v>19</v>
+      </c>
+      <c r="C997" t="s">
+        <v>20</v>
+      </c>
+      <c r="E997"/>
+      <c r="F997">
+        <v>2778276547</v>
+      </c>
+      <c r="G997" s="2">
+        <v>1784656755654240</v>
+      </c>
+      <c r="H997" t="s">
+        <v>195</v>
+      </c>
+      <c r="I997" t="s">
+        <v>80</v>
+      </c>
+      <c r="J997" t="s">
+        <v>197</v>
+      </c>
+      <c r="K997" t="s">
+        <v>25</v>
+      </c>
+      <c r="L997" t="s">
+        <v>132</v>
+      </c>
+      <c r="N997" t="s">
+        <v>22</v>
+      </c>
+      <c r="O997">
+        <v>16</v>
+      </c>
+      <c r="R997" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S997" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="998" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A998" s="1">
+        <v>46224.625196759262</v>
+      </c>
+      <c r="B998" t="s">
+        <v>19</v>
+      </c>
+      <c r="C998" t="s">
+        <v>20</v>
+      </c>
+      <c r="E998"/>
+      <c r="F998">
+        <v>2778276609</v>
+      </c>
+      <c r="G998" s="2">
+        <v>1784656817656550</v>
+      </c>
+      <c r="H998" t="s">
+        <v>195</v>
+      </c>
+      <c r="I998" t="s">
+        <v>80</v>
+      </c>
+      <c r="J998" t="s">
+        <v>197</v>
+      </c>
+      <c r="K998" t="s">
+        <v>25</v>
+      </c>
+      <c r="L998" t="s">
+        <v>39</v>
+      </c>
+      <c r="N998" t="s">
+        <v>24</v>
+      </c>
+      <c r="O998">
+        <v>16</v>
+      </c>
+      <c r="R998" s="3">
+        <v>2.0717592592592593E-3</v>
+      </c>
+      <c r="S998" s="3">
+        <v>1.9328703703703704E-3</v>
+      </c>
+    </row>
+    <row r="999" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A999" s="1">
+        <v>46224.627881944441</v>
+      </c>
+      <c r="B999" t="s">
+        <v>19</v>
+      </c>
+      <c r="C999" t="s">
+        <v>20</v>
+      </c>
+      <c r="E999"/>
+      <c r="F999">
+        <v>2758685587</v>
+      </c>
+      <c r="G999" s="2">
+        <v>1784657049662240</v>
+      </c>
+      <c r="H999" t="s">
+        <v>195</v>
+      </c>
+      <c r="I999" t="s">
+        <v>166</v>
+      </c>
+      <c r="J999" t="s">
+        <v>197</v>
+      </c>
+      <c r="K999" t="s">
+        <v>25</v>
+      </c>
+      <c r="L999" t="s">
+        <v>28</v>
+      </c>
+      <c r="N999" t="s">
+        <v>24</v>
+      </c>
+      <c r="O999">
+        <v>16</v>
+      </c>
+      <c r="R999" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S999" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1000" s="1">
+        <v>46224.62809027778</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1000"/>
+      <c r="F1000">
+        <v>2758685605</v>
+      </c>
+      <c r="G1000" s="2">
+        <v>1784657067662640</v>
+      </c>
+      <c r="H1000" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1000" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1000" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1000" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1000" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1000" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1000">
+        <v>16</v>
+      </c>
+      <c r="R1000" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1000" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1001" s="1">
+        <v>46224.628668981481</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1001"/>
+      <c r="F1001">
+        <v>2751610253</v>
+      </c>
+      <c r="G1001" s="2">
+        <v>1784657117663440</v>
+      </c>
+      <c r="H1001" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1001" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1001" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1001" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1001" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1001" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1001">
+        <v>16</v>
+      </c>
+      <c r="R1001" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="S1001" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1002" s="1">
+        <v>46224.62909722222</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1002"/>
+      <c r="F1002">
+        <v>2751610290</v>
+      </c>
+      <c r="G1002" s="2">
+        <v>1784657154664460</v>
+      </c>
+      <c r="H1002" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1002" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1002" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1002" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1002" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1002">
+        <v>19</v>
+      </c>
+      <c r="R1002" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1002" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1003" s="1">
+        <v>46224.629548611112</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1003"/>
+      <c r="F1003">
+        <v>2768656937</v>
+      </c>
+      <c r="G1003" s="2">
+        <v>1784657193665550</v>
+      </c>
+      <c r="H1003" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1003" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1003" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1003" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1003" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1003" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1003">
+        <v>16</v>
+      </c>
+      <c r="R1003" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1003" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1004" s="1">
+        <v>46224.629884259259</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1004"/>
+      <c r="F1004">
+        <v>2768656966</v>
+      </c>
+      <c r="G1004" s="2">
+        <v>1784657222666290</v>
+      </c>
+      <c r="H1004" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1004" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1004" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1004" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1004" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1004" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1004">
+        <v>16</v>
+      </c>
+      <c r="R1004" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1004" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1005" s="1">
+        <v>46224.63045138889</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1005"/>
+      <c r="F1005">
+        <v>2774719246</v>
+      </c>
+      <c r="G1005" s="2">
+        <v>1784657271667880</v>
+      </c>
+      <c r="H1005" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1005" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1005" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1005" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1005" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1005">
+        <v>19</v>
+      </c>
+      <c r="R1005" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="S1005" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1006" s="1">
+        <v>46224.630752314813</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1006"/>
+      <c r="F1006">
+        <v>2774719272</v>
+      </c>
+      <c r="G1006" s="2">
+        <v>1784657297668630</v>
+      </c>
+      <c r="H1006" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1006" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1006" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1006" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1006" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1006">
+        <v>19</v>
+      </c>
+      <c r="R1006" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="S1006" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1007" s="1">
+        <v>46224.631620370368</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1007"/>
+      <c r="F1007">
+        <v>2760496361</v>
+      </c>
+      <c r="G1007" s="2">
+        <v>1784657372671490</v>
+      </c>
+      <c r="H1007" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1007" t="s">
+        <v>173</v>
+      </c>
+      <c r="J1007" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1007" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1007" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1007" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1007">
+        <v>16</v>
+      </c>
+      <c r="R1007" s="3">
+        <v>4.0046296296296297E-3</v>
+      </c>
+      <c r="S1007" s="3">
+        <v>3.6689814814814814E-3</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1008" s="1">
+        <v>46224.638043981482</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1008"/>
+      <c r="F1008">
+        <v>2754056043</v>
+      </c>
+      <c r="G1008" s="2">
+        <v>1784657895690470</v>
+      </c>
+      <c r="H1008" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1008" t="s">
+        <v>174</v>
+      </c>
+      <c r="J1008" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1008" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1008" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1008">
+        <v>17</v>
+      </c>
+      <c r="R1008" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1008" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1009" s="1">
+        <v>46224.638356481482</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1009"/>
+      <c r="F1009">
+        <v>2754056083</v>
+      </c>
+      <c r="G1009" s="2">
+        <v>1784657935691940</v>
+      </c>
+      <c r="H1009" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1009" t="s">
+        <v>174</v>
+      </c>
+      <c r="J1009" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1009" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1009" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1009">
+        <v>19</v>
+      </c>
+      <c r="R1009" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1009" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1010" s="1">
+        <v>46224.638738425929</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1010"/>
+      <c r="F1010">
+        <v>2774758917</v>
+      </c>
+      <c r="G1010" s="2">
+        <v>1784657987693680</v>
+      </c>
+      <c r="H1010" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1010" t="s">
+        <v>176</v>
+      </c>
+      <c r="J1010" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1010" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1010" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1010" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1010">
+        <v>16</v>
+      </c>
+      <c r="R1010" s="3">
+        <v>1.5162037037037036E-3</v>
+      </c>
+      <c r="S1010" s="3">
+        <v>1.4467592592592592E-3</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1011" s="1">
+        <v>46224.641493055555</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1011"/>
+      <c r="F1011">
+        <v>2773107675</v>
+      </c>
+      <c r="G1011" s="2">
+        <v>1784658225700130</v>
+      </c>
+      <c r="H1011" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1011" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1011" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1011" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1011" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1011">
+        <v>19</v>
+      </c>
+      <c r="R1011" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1011" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1012" s="1">
+        <v>46224.641736111109</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1012" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1012"/>
+      <c r="F1012">
+        <v>2773107696</v>
+      </c>
+      <c r="G1012" s="2">
+        <v>1784658246700870</v>
+      </c>
+      <c r="H1012" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1012" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1012" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1012" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1012" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1012">
+        <v>19</v>
+      </c>
+      <c r="R1012" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1012" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1013" s="1">
+        <v>46224.647280092591</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1013"/>
+      <c r="F1013">
+        <v>2768164209</v>
+      </c>
+      <c r="G1013" s="2">
+        <v>1784658725711690</v>
+      </c>
+      <c r="H1013" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1013" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1013" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1013" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1013" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1013">
+        <v>19</v>
+      </c>
+      <c r="R1013" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1013" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1014" s="1">
+        <v>46224.647800925923</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1014"/>
+      <c r="F1014">
+        <v>2768164254</v>
+      </c>
+      <c r="G1014" s="2">
+        <v>1784658770712680</v>
+      </c>
+      <c r="H1014" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1014" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1014" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1014" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1014" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1014">
+        <v>16</v>
+      </c>
+      <c r="R1014" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="S1014" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1015" s="1">
+        <v>46224.648287037038</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1015"/>
+      <c r="F1015">
+        <v>2768958887</v>
+      </c>
+      <c r="G1015" s="2">
+        <v>1784658812713730</v>
+      </c>
+      <c r="H1015" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1015" t="s">
+        <v>179</v>
+      </c>
+      <c r="J1015" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1015" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1015" t="s">
+        <v>132</v>
+      </c>
+      <c r="N1015" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1015">
+        <v>16</v>
+      </c>
+      <c r="R1015" s="3">
+        <v>1.5046296296296296E-3</v>
+      </c>
+      <c r="S1015" s="3">
+        <v>1.4814814814814814E-3</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1016" s="1">
+        <v>46224.65016203704</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1016"/>
+      <c r="F1016">
+        <v>2768959048</v>
+      </c>
+      <c r="G1016" s="2">
+        <v>1784658974718800</v>
+      </c>
+      <c r="H1016" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1016" t="s">
+        <v>179</v>
+      </c>
+      <c r="J1016" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1016" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1016" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1016" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1016">
+        <v>16</v>
+      </c>
+      <c r="R1016" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="S1016" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1017" s="1">
+        <v>46224.652488425927</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1017"/>
+      <c r="F1017">
+        <v>2781770374</v>
+      </c>
+      <c r="G1017" s="2">
+        <v>1784659175723950</v>
+      </c>
+      <c r="H1017" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1017" t="s">
+        <v>180</v>
+      </c>
+      <c r="J1017" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1017" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1017" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1017">
+        <v>19</v>
+      </c>
+      <c r="R1017" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S1017" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1018" s="1">
+        <v>46224.652916666666</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1018" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1018"/>
+      <c r="F1018">
+        <v>2781770411</v>
+      </c>
+      <c r="G1018" s="2">
+        <v>1784659212725250</v>
+      </c>
+      <c r="H1018" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1018" t="s">
+        <v>180</v>
+      </c>
+      <c r="J1018" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1018" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1018" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1018" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1018">
+        <v>16</v>
+      </c>
+      <c r="R1018" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S1018" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1019" s="1">
+        <v>46224.653611111113</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1019"/>
+      <c r="F1019">
+        <v>2782579885</v>
+      </c>
+      <c r="G1019" s="2">
+        <v>1784659272726410</v>
+      </c>
+      <c r="H1019" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1019" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1019" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1019" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1019" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1019" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1019">
+        <v>16</v>
+      </c>
+      <c r="R1019" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="S1019" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1020" s="1">
+        <v>46224.654097222221</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1020"/>
+      <c r="F1020">
+        <v>2782579927</v>
+      </c>
+      <c r="G1020" s="2">
+        <v>1784659314727770</v>
+      </c>
+      <c r="H1020" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1020" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1020" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1020" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1020" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1020" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1020">
+        <v>16</v>
+      </c>
+      <c r="R1020" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1020" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1021" s="1">
+        <v>46224.654861111114</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1021"/>
+      <c r="F1021">
+        <v>2760779559</v>
+      </c>
+      <c r="G1021" s="2">
+        <v>1784659380729300</v>
+      </c>
+      <c r="H1021" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1021" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1021" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1021" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1021" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1021">
+        <v>19</v>
+      </c>
+      <c r="R1021" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1021" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1022" s="1">
+        <v>46224.654976851853</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1022" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1022"/>
+      <c r="F1022">
+        <v>2760779568</v>
+      </c>
+      <c r="G1022" s="2">
+        <v>1784659390729660</v>
+      </c>
+      <c r="H1022" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1022" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1022" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1022" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1022" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1022">
+        <v>19</v>
+      </c>
+      <c r="R1022" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1022" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1023" s="1">
+        <v>46224.655173611114</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1023"/>
+      <c r="F1023">
+        <v>2760779585</v>
+      </c>
+      <c r="G1023" s="2">
+        <v>1784659407730050</v>
+      </c>
+      <c r="H1023" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1023" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1023" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1023" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1023" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1023">
+        <v>19</v>
+      </c>
+      <c r="R1023" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1023" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1024" s="1">
+        <v>46224.655497685184</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1024" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1024"/>
+      <c r="F1024">
+        <v>2783461184</v>
+      </c>
+      <c r="G1024" s="2">
+        <v>1784659435731210</v>
+      </c>
+      <c r="H1024" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1024" t="s">
+        <v>181</v>
+      </c>
+      <c r="J1024" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1024" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1024" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1024">
+        <v>19</v>
+      </c>
+      <c r="R1024" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="S1024" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1025" s="1">
+        <v>46224.657384259262</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1025"/>
+      <c r="F1025">
+        <v>2783461347</v>
+      </c>
+      <c r="G1025" s="2">
+        <v>1784659598736000</v>
+      </c>
+      <c r="H1025" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1025" t="s">
+        <v>181</v>
+      </c>
+      <c r="J1025" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1025" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1025" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1025">
+        <v>19</v>
+      </c>
+      <c r="R1025" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S1025" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1026" s="1">
+        <v>46224.657731481479</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1026"/>
+      <c r="F1026">
+        <v>2783461377</v>
+      </c>
+      <c r="G1026" s="2">
+        <v>1784659628736700</v>
+      </c>
+      <c r="H1026" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1026" t="s">
+        <v>181</v>
+      </c>
+      <c r="J1026" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1026" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1026" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1026">
+        <v>19</v>
+      </c>
+      <c r="R1026" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="S1026" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1027" s="1">
+        <v>46224.658750000002</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1027"/>
+      <c r="F1027">
+        <v>2782803765</v>
+      </c>
+      <c r="G1027" s="2">
+        <v>1784659700738470</v>
+      </c>
+      <c r="H1027" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1027" t="s">
+        <v>182</v>
+      </c>
+      <c r="J1027" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1027" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1027" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1027">
+        <v>17</v>
+      </c>
+      <c r="R1027" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1027" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1028" s="1">
+        <v>46224.659085648149</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1028"/>
+      <c r="F1028">
+        <v>2782803788</v>
+      </c>
+      <c r="G1028" s="2">
+        <v>1784659723739210</v>
+      </c>
+      <c r="H1028" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1028" t="s">
+        <v>182</v>
+      </c>
+      <c r="J1028" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1028" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1028" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1028">
+        <v>17</v>
+      </c>
+      <c r="R1028" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1028" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1029" s="1">
+        <v>46224.659502314818</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1029"/>
+      <c r="F1029">
+        <v>2753078367</v>
+      </c>
+      <c r="G1029" s="2">
+        <v>1784659781741270</v>
+      </c>
+      <c r="H1029" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1029" t="s">
+        <v>183</v>
+      </c>
+      <c r="J1029" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1029" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1029" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1029">
+        <v>19</v>
+      </c>
+      <c r="R1029" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1029" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1030" s="1">
+        <v>46224.659641203703</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1030"/>
+      <c r="F1030">
+        <v>2753078379</v>
+      </c>
+      <c r="G1030" s="2">
+        <v>1784659793741700</v>
+      </c>
+      <c r="H1030" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1030" t="s">
+        <v>183</v>
+      </c>
+      <c r="J1030" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1030" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1030" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1030">
+        <v>19</v>
+      </c>
+      <c r="R1030" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1030" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1031" s="1">
+        <v>46224.659756944442</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1031"/>
+      <c r="F1031">
+        <v>2753078389</v>
+      </c>
+      <c r="G1031" s="2">
+        <v>1784659803742310</v>
+      </c>
+      <c r="H1031" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1031" t="s">
+        <v>183</v>
+      </c>
+      <c r="J1031" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1031" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1031" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1031">
+        <v>19</v>
+      </c>
+      <c r="R1031" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="S1031" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1032" s="1">
+        <v>46224.669791666667</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1032"/>
+      <c r="F1032">
+        <v>2769523882</v>
+      </c>
+      <c r="G1032" s="2">
+        <v>1784660670764970</v>
+      </c>
+      <c r="H1032" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1032" t="s">
+        <v>184</v>
+      </c>
+      <c r="J1032" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1032" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1032" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1032" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1032">
+        <v>16</v>
+      </c>
+      <c r="R1032" s="3">
+        <v>2.0138888888888888E-3</v>
+      </c>
+      <c r="S1032" s="3">
+        <v>1.9212962962962964E-3</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1033" s="1">
+        <v>46224.672280092593</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1033"/>
+      <c r="F1033">
+        <v>2769424594</v>
+      </c>
+      <c r="G1033" s="2">
+        <v>1784660885771930</v>
+      </c>
+      <c r="H1033" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1033" t="s">
+        <v>185</v>
+      </c>
+      <c r="J1033" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1033" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1033" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1033" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1033">
+        <v>16</v>
+      </c>
+      <c r="R1033" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="S1033" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1034" s="1">
+        <v>46224.672997685186</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1034"/>
+      <c r="F1034">
+        <v>2769424656</v>
+      </c>
+      <c r="G1034" s="2">
+        <v>1784660947774230</v>
+      </c>
+      <c r="H1034" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1034" t="s">
+        <v>185</v>
+      </c>
+      <c r="J1034" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1034" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1034" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1034" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1034">
+        <v>16</v>
+      </c>
+      <c r="R1034" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1034" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1035" s="1">
+        <v>46224.673506944448</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1035"/>
+      <c r="F1035">
+        <v>2781377349</v>
+      </c>
+      <c r="G1035" s="2">
+        <v>1784660991775190</v>
+      </c>
+      <c r="H1035" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1035" t="s">
+        <v>186</v>
+      </c>
+      <c r="J1035" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1035" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1035" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1035">
+        <v>19</v>
+      </c>
+      <c r="R1035" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S1035" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1036" s="1">
+        <v>46224.673877314817</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1036" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1036"/>
+      <c r="F1036">
+        <v>2781377381</v>
+      </c>
+      <c r="G1036" s="2">
+        <v>1784661023776160</v>
+      </c>
+      <c r="H1036" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1036" t="s">
+        <v>186</v>
+      </c>
+      <c r="J1036" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1036" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1036" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1036">
+        <v>19</v>
+      </c>
+      <c r="R1036" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1036" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1037" s="1">
+        <v>46224.675300925926</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1037" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1037"/>
+      <c r="F1037">
+        <v>2781377504</v>
+      </c>
+      <c r="G1037" s="2">
+        <v>1784661146780510</v>
+      </c>
+      <c r="H1037" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1037" t="s">
+        <v>186</v>
+      </c>
+      <c r="J1037" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1037" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1037" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1037">
+        <v>19</v>
+      </c>
+      <c r="R1037" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1037" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1038" s="1">
+        <v>46224.677175925928</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1038"/>
+      <c r="F1038">
+        <v>1822942347</v>
+      </c>
+      <c r="G1038" s="2">
+        <v>1784661308785680</v>
+      </c>
+      <c r="H1038" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1038" t="s">
+        <v>187</v>
+      </c>
+      <c r="J1038" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1038" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1038" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1038" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1038">
+        <v>16</v>
+      </c>
+      <c r="R1038" s="3">
+        <v>1.2152777777777778E-3</v>
+      </c>
+      <c r="S1038" s="3">
+        <v>1.2037037037037038E-3</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1039" s="1">
+        <v>46224.679189814815</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1039" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1039"/>
+      <c r="F1039">
+        <v>2776178571</v>
+      </c>
+      <c r="G1039" s="2">
+        <v>1784661482791290</v>
+      </c>
+      <c r="H1039" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1039" t="s">
+        <v>188</v>
+      </c>
+      <c r="J1039" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1039" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1039" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1039" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1039">
+        <v>16</v>
+      </c>
+      <c r="R1039" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S1039" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1040" s="1">
+        <v>46224.681168981479</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1040" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1040"/>
+      <c r="F1040">
+        <v>2776178743</v>
+      </c>
+      <c r="G1040" s="2">
+        <v>1784661653796140</v>
+      </c>
+      <c r="H1040" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1040" t="s">
+        <v>188</v>
+      </c>
+      <c r="J1040" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1040" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1040" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1040">
+        <v>19</v>
+      </c>
+      <c r="R1040" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S1040" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1041" s="1">
+        <v>46224.683969907404</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1041"/>
+      <c r="F1041">
+        <v>2781461614</v>
+      </c>
+      <c r="G1041" s="2">
+        <v>1784661895803860</v>
+      </c>
+      <c r="H1041" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1041" t="s">
+        <v>189</v>
+      </c>
+      <c r="J1041" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1041" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1041" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1041" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1041">
+        <v>16</v>
+      </c>
+      <c r="R1041" s="3">
+        <v>1.4583333333333334E-3</v>
+      </c>
+      <c r="S1041" s="3">
+        <v>1.3888888888888889E-3</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1042" s="1">
+        <v>46224.686805555553</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1042"/>
+      <c r="F1042">
+        <v>2772742217</v>
+      </c>
+      <c r="G1042" s="2">
+        <v>1784662086809930</v>
+      </c>
+      <c r="H1042" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1042" t="s">
+        <v>190</v>
+      </c>
+      <c r="J1042" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1042" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1042" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1042">
+        <v>19</v>
+      </c>
+      <c r="R1042" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1042" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1043" s="1">
+        <v>46224.687037037038</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1043"/>
+      <c r="F1043">
+        <v>2772742291</v>
+      </c>
+      <c r="G1043" s="2">
+        <v>1784662160812450</v>
+      </c>
+      <c r="H1043" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1043" t="s">
+        <v>190</v>
+      </c>
+      <c r="J1043" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1043" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1043" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1043" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1043">
+        <v>16</v>
+      </c>
+      <c r="R1043" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S1043" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1044" s="1">
+        <v>46224.688611111109</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1044"/>
+      <c r="F1044">
+        <v>2770527059</v>
+      </c>
+      <c r="G1044" s="2">
+        <v>1784662235815270</v>
+      </c>
+      <c r="H1044" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1044" t="s">
+        <v>191</v>
+      </c>
+      <c r="J1044" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1044" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1044" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1044">
+        <v>19</v>
+      </c>
+      <c r="R1044" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1044" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1045" s="1">
+        <v>46224.688692129632</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1045"/>
+      <c r="F1045">
+        <v>2770527127</v>
+      </c>
+      <c r="G1045" s="2">
+        <v>1784662303817310</v>
+      </c>
+      <c r="H1045" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1045" t="s">
+        <v>191</v>
+      </c>
+      <c r="J1045" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1045" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1045" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1045">
+        <v>19</v>
+      </c>
+      <c r="R1045" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="S1045" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1046" s="1">
+        <v>46224.689560185187</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1046"/>
+      <c r="F1046">
+        <v>2783195824</v>
+      </c>
+      <c r="G1046" s="2">
+        <v>1784662378819720</v>
+      </c>
+      <c r="H1046" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1046" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1046" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1046" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1046" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1046">
+        <v>19</v>
+      </c>
+      <c r="R1046" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="S1046" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1047" s="1">
+        <v>46224.690138888887</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1047"/>
+      <c r="F1047">
+        <v>2783195874</v>
+      </c>
+      <c r="G1047" s="2">
+        <v>1784662428820790</v>
+      </c>
+      <c r="H1047" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1047" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1047" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1047" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1047" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1047" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1047">
+        <v>16</v>
+      </c>
+      <c r="R1047" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1047" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1048" s="1">
+        <v>46224.694016203706</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1048"/>
+      <c r="F1048">
+        <v>2750317749</v>
+      </c>
+      <c r="G1048" s="2">
+        <v>1784662763834050</v>
+      </c>
+      <c r="H1048" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1048" t="s">
+        <v>192</v>
+      </c>
+      <c r="J1048" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1048" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1048" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1048" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1048">
+        <v>16</v>
+      </c>
+      <c r="R1048" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="S1048" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1049" s="1">
+        <v>46224.694363425922</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1049"/>
+      <c r="F1049">
+        <v>2750317779</v>
+      </c>
+      <c r="G1049" s="2">
+        <v>1784662793835170</v>
+      </c>
+      <c r="H1049" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1049" t="s">
+        <v>192</v>
+      </c>
+      <c r="J1049" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1049" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1049" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1049" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1049">
+        <v>16</v>
+      </c>
+      <c r="R1049" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1049" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1050" s="1">
+        <v>46224.694594907407</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1050"/>
+      <c r="F1050">
+        <v>2750317799</v>
+      </c>
+      <c r="G1050" s="2">
+        <v>1784662813836300</v>
+      </c>
+      <c r="H1050" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1050" t="s">
+        <v>192</v>
+      </c>
+      <c r="J1050" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1050" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1050" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1050">
+        <v>19</v>
+      </c>
+      <c r="R1050" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="S1050" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S731" xr:uid="{D24DB4E9-414F-485A-A3F2-E34A8848786F}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Arquivos/nao_atualizaveis/Ativo_Prospecção IEL/Discagem_Ativo_Prospecção_IEL.xlsx
+++ b/Arquivos/nao_atualizaveis/Ativo_Prospecção IEL/Discagem_Ativo_Prospecção_IEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Ativo_Prospecção IEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD48DDFC-F0C6-4642-AEB4-C546785828E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D75773-CC1F-4B1D-8ECF-1B84121D2A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8576016-ED65-4244-9F24-F723354B3EF0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C8576016-ED65-4244-9F24-F723354B3EF0}"/>
   </bookViews>
   <sheets>
     <sheet name="chamadas_16-07-2026_172506" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9110" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10929" uniqueCount="224">
   <si>
     <t>DATA</t>
   </si>
@@ -692,6 +692,9 @@
   </si>
   <si>
     <t>Falhou</t>
+  </si>
+  <si>
+    <t>(21) 99738-4115</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D24DB4E9-414F-485A-A3F2-E34A8848786F}">
-  <dimension ref="A1:S1050"/>
+  <dimension ref="A1:S1277"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -52590,6 +52593,9813 @@
         <v>23</v>
       </c>
     </row>
+    <row r="1051" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1051" s="1">
+        <v>46225.388182870367</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1051"/>
+      <c r="F1051">
+        <v>2779961871</v>
+      </c>
+      <c r="G1051" s="2">
+        <v>178472273968571</v>
+      </c>
+      <c r="H1051" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1051" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1051" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1051" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1051" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1051">
+        <v>19</v>
+      </c>
+      <c r="R1051" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1051" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1052" s="1">
+        <v>46225.388796296298</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1052"/>
+      <c r="F1052">
+        <v>2779961916</v>
+      </c>
+      <c r="G1052" s="2">
+        <v>178472278369461</v>
+      </c>
+      <c r="H1052" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1052" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1052" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1052" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1052" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1052">
+        <v>17</v>
+      </c>
+      <c r="R1052" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1052" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1053" s="1">
+        <v>46225.38957175926</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1053"/>
+      <c r="F1053">
+        <v>2779961942</v>
+      </c>
+      <c r="G1053" s="2">
+        <v>178472281069971</v>
+      </c>
+      <c r="H1053" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1053" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1053" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1053" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1053" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1053">
+        <v>19</v>
+      </c>
+      <c r="R1053" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1053" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1054" s="1">
+        <v>46225.389710648145</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1054"/>
+      <c r="F1054">
+        <v>2779962003</v>
+      </c>
+      <c r="G1054" s="2">
+        <v>178472287171521</v>
+      </c>
+      <c r="H1054" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1054" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1054" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1054" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1054" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1054">
+        <v>19</v>
+      </c>
+      <c r="R1054" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="S1054" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1055" s="1">
+        <v>46225.390555555554</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1055" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1055"/>
+      <c r="F1055">
+        <v>24766526627</v>
+      </c>
+      <c r="G1055" s="2">
+        <v>178472294473711</v>
+      </c>
+      <c r="H1055" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1055">
+        <v>5522981803628</v>
+      </c>
+      <c r="J1055" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1055" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1055" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1055">
+        <v>21</v>
+      </c>
+      <c r="R1055" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1055" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1056" s="1">
+        <v>46225.391018518516</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1056"/>
+      <c r="F1056">
+        <v>2766526635</v>
+      </c>
+      <c r="G1056" s="2">
+        <v>178472298475061</v>
+      </c>
+      <c r="H1056" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1056" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1056" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1056" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1056" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1056" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1056">
+        <v>16</v>
+      </c>
+      <c r="R1056" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1056" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1057" s="1">
+        <v>46225.391250000001</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1057" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1057"/>
+      <c r="F1057">
+        <v>2766526654</v>
+      </c>
+      <c r="G1057" s="2">
+        <v>178472300475731</v>
+      </c>
+      <c r="H1057" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1057" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1057" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1057" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1057" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1057" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1057">
+        <v>16</v>
+      </c>
+      <c r="R1057" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1057" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1058" s="1">
+        <v>46225.39166666667</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1058" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1058"/>
+      <c r="F1058">
+        <v>2766526690</v>
+      </c>
+      <c r="G1058" s="2">
+        <v>178472304076991</v>
+      </c>
+      <c r="H1058" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1058" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1058" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1058" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1058" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1058" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1058">
+        <v>16</v>
+      </c>
+      <c r="R1058" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1058" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1059" s="1">
+        <v>46225.39203703704</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1059"/>
+      <c r="F1059">
+        <v>2784500491</v>
+      </c>
+      <c r="G1059" s="2">
+        <v>178472307277871</v>
+      </c>
+      <c r="H1059" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1059" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1059" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1059" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1059" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1059" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1059">
+        <v>16</v>
+      </c>
+      <c r="R1059" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1059" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1060" s="1">
+        <v>46225.392210648148</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1060" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1060"/>
+      <c r="F1060">
+        <v>2784500506</v>
+      </c>
+      <c r="G1060" s="2">
+        <v>178472308778391</v>
+      </c>
+      <c r="H1060" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1060" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1060" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1060" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1060" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1060" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1060">
+        <v>16</v>
+      </c>
+      <c r="R1060" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1060" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1061" s="1">
+        <v>46225.393263888887</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1061"/>
+      <c r="F1061">
+        <v>2704908557</v>
+      </c>
+      <c r="G1061" s="2">
+        <v>178472317281001</v>
+      </c>
+      <c r="H1061" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1061" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1061" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1061" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1061" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1061">
+        <v>17</v>
+      </c>
+      <c r="R1061" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1061" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1062" s="1">
+        <v>46225.393437500003</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1062"/>
+      <c r="F1062">
+        <v>2704908573</v>
+      </c>
+      <c r="G1062" s="2">
+        <v>178472318881311</v>
+      </c>
+      <c r="H1062" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1062" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1062" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1062" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1062" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1062">
+        <v>17</v>
+      </c>
+      <c r="R1062" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1062" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1063" s="1">
+        <v>46225.393645833334</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1063" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1063"/>
+      <c r="F1063">
+        <v>2704908592</v>
+      </c>
+      <c r="G1063" s="2">
+        <v>178472320782051</v>
+      </c>
+      <c r="H1063" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1063" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1063" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1063" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1063" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1063">
+        <v>17</v>
+      </c>
+      <c r="R1063" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1063" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1064" s="1">
+        <v>46225.394016203703</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1064"/>
+      <c r="F1064">
+        <v>2783356614</v>
+      </c>
+      <c r="G1064" s="2">
+        <v>178472324383681</v>
+      </c>
+      <c r="H1064" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1064" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1064" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1064" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1064" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1064">
+        <v>19</v>
+      </c>
+      <c r="R1064" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1064" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1065" s="1">
+        <v>46225.394212962965</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1065" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1065"/>
+      <c r="F1065">
+        <v>2783356631</v>
+      </c>
+      <c r="G1065" s="2">
+        <v>178472326084171</v>
+      </c>
+      <c r="H1065" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1065" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1065" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1065" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1065" t="s">
+        <v>175</v>
+      </c>
+      <c r="N1065" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1065">
+        <v>16</v>
+      </c>
+      <c r="R1065" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="S1065" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1066" s="1">
+        <v>46225.394861111112</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1066"/>
+      <c r="F1066">
+        <v>2783356687</v>
+      </c>
+      <c r="G1066" s="2">
+        <v>178472331685881</v>
+      </c>
+      <c r="H1066" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1066" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1066" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1066" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1066" t="s">
+        <v>175</v>
+      </c>
+      <c r="N1066" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1066">
+        <v>16</v>
+      </c>
+      <c r="R1066" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="S1066" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1067" s="1">
+        <v>46225.395775462966</v>
+      </c>
+      <c r="B1067" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1067" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1067"/>
+      <c r="F1067">
+        <v>2782107531</v>
+      </c>
+      <c r="G1067" s="2">
+        <v>178472339588611</v>
+      </c>
+      <c r="H1067" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1067" t="s">
+        <v>223</v>
+      </c>
+      <c r="J1067" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1067" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1067" t="s">
+        <v>203</v>
+      </c>
+      <c r="N1067" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1067">
+        <v>16</v>
+      </c>
+      <c r="R1067" s="3">
+        <v>8.6805555555555551E-4</v>
+      </c>
+      <c r="S1067" s="3">
+        <v>7.5231481481481482E-4</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1068" s="1">
+        <v>46225.397314814814</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1068"/>
+      <c r="F1068">
+        <v>2753166251</v>
+      </c>
+      <c r="G1068" s="2">
+        <v>178472352891811</v>
+      </c>
+      <c r="H1068" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1068" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1068" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1068" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1068" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1068" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1068">
+        <v>16</v>
+      </c>
+      <c r="R1068" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="S1068" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1069" s="1">
+        <v>46225.397951388892</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1069"/>
+      <c r="F1069">
+        <v>2753166306</v>
+      </c>
+      <c r="G1069" s="2">
+        <v>178472358392921</v>
+      </c>
+      <c r="H1069" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1069" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1069" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1069" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1069" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1069" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1069">
+        <v>16</v>
+      </c>
+      <c r="R1069" s="3">
+        <v>1.9328703703703704E-3</v>
+      </c>
+      <c r="S1069" s="3">
+        <v>1.6435185185185185E-3</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1070" s="1">
+        <v>46225.401597222219</v>
+      </c>
+      <c r="B1070" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1070"/>
+      <c r="F1070">
+        <v>2750339423</v>
+      </c>
+      <c r="G1070" s="2">
+        <v>1784723898100730</v>
+      </c>
+      <c r="H1070" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1070" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1070" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1070" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1070" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1070">
+        <v>19</v>
+      </c>
+      <c r="R1070" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1070" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1071" s="1">
+        <v>46225.401724537034</v>
+      </c>
+      <c r="B1071" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1071"/>
+      <c r="F1071">
+        <v>2750339434</v>
+      </c>
+      <c r="G1071" s="2">
+        <v>1784723909101220</v>
+      </c>
+      <c r="H1071" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1071" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1071" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1071" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1071" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1071">
+        <v>19</v>
+      </c>
+      <c r="R1071" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1071" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1072" s="1">
+        <v>46225.401898148149</v>
+      </c>
+      <c r="B1072" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1072"/>
+      <c r="F1072">
+        <v>2750339449</v>
+      </c>
+      <c r="G1072" s="2">
+        <v>1784723924101760</v>
+      </c>
+      <c r="H1072" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1072" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1072" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1072" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1072" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1072">
+        <v>19</v>
+      </c>
+      <c r="R1072" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1072" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1073" s="1">
+        <v>46225.402430555558</v>
+      </c>
+      <c r="B1073" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1073" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1073"/>
+      <c r="F1073">
+        <v>2757890823</v>
+      </c>
+      <c r="G1073" s="2">
+        <v>1784723970103310</v>
+      </c>
+      <c r="H1073" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1073" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1073" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1073" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1073" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1073" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1073">
+        <v>16</v>
+      </c>
+      <c r="R1073" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1073" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1074" s="1">
+        <v>46225.402673611112</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1074"/>
+      <c r="F1074">
+        <v>2757890844</v>
+      </c>
+      <c r="G1074" s="2">
+        <v>1784723991104140</v>
+      </c>
+      <c r="H1074" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1074" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1074" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1074" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1074" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1074" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1074">
+        <v>16</v>
+      </c>
+      <c r="R1074" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1074" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1075" s="1">
+        <v>46225.402928240743</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1075"/>
+      <c r="F1075">
+        <v>2757890866</v>
+      </c>
+      <c r="G1075" s="2">
+        <v>1784724013104920</v>
+      </c>
+      <c r="H1075" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1075" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1075" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1075" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1075" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1075">
+        <v>19</v>
+      </c>
+      <c r="R1075" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1075" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1076" s="1">
+        <v>46225.403449074074</v>
+      </c>
+      <c r="B1076" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1076"/>
+      <c r="F1076">
+        <v>2743732052</v>
+      </c>
+      <c r="G1076" s="2">
+        <v>1784724058106320</v>
+      </c>
+      <c r="H1076" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1076" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1076" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1076" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1076" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1076">
+        <v>19</v>
+      </c>
+      <c r="R1076" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="S1076" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1077" s="1">
+        <v>46225.40388888889</v>
+      </c>
+      <c r="B1077" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1077"/>
+      <c r="F1077">
+        <v>2743732090</v>
+      </c>
+      <c r="G1077" s="2">
+        <v>1784724096107630</v>
+      </c>
+      <c r="H1077" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1077" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1077" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1077" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1077" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1077">
+        <v>19</v>
+      </c>
+      <c r="R1077" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="S1077" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1078" s="1">
+        <v>46225.404293981483</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1078"/>
+      <c r="F1078">
+        <v>2743732125</v>
+      </c>
+      <c r="G1078" s="2">
+        <v>1784724131108920</v>
+      </c>
+      <c r="H1078" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1078" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1078" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1078" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1078" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1078">
+        <v>19</v>
+      </c>
+      <c r="R1078" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1078" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1079" s="1">
+        <v>46225.405069444445</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1079"/>
+      <c r="F1079">
+        <v>2758766696</v>
+      </c>
+      <c r="G1079" s="2">
+        <v>1784724198110250</v>
+      </c>
+      <c r="H1079" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1079" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1079" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1079" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1079" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1079" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1079">
+        <v>16</v>
+      </c>
+      <c r="R1079" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S1079" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1080" s="1">
+        <v>46225.405439814815</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1080"/>
+      <c r="F1080">
+        <v>2758766728</v>
+      </c>
+      <c r="G1080" s="2">
+        <v>1784724230111170</v>
+      </c>
+      <c r="H1080" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1080" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1080" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1080" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1080" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1080">
+        <v>19</v>
+      </c>
+      <c r="R1080" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1080" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1081" s="1">
+        <v>46225.405671296299</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1081"/>
+      <c r="F1081">
+        <v>2758766748</v>
+      </c>
+      <c r="G1081" s="2">
+        <v>1784724250111680</v>
+      </c>
+      <c r="H1081" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1081" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1081" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1081" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1081" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1081">
+        <v>19</v>
+      </c>
+      <c r="R1081" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1081" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1082" s="1">
+        <v>46225.40625</v>
+      </c>
+      <c r="B1082" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1082"/>
+      <c r="F1082">
+        <v>2760314033</v>
+      </c>
+      <c r="G1082" s="2">
+        <v>1784724300113000</v>
+      </c>
+      <c r="H1082" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1082" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1082" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1082" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1082" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1082">
+        <v>19</v>
+      </c>
+      <c r="R1082" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="S1082" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1083" s="1">
+        <v>46225.406817129631</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1083"/>
+      <c r="F1083">
+        <v>2760314082</v>
+      </c>
+      <c r="G1083" s="2">
+        <v>1784724349113800</v>
+      </c>
+      <c r="H1083" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1083" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1083" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1083" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1083" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1083">
+        <v>19</v>
+      </c>
+      <c r="R1083" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1083" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1084" s="1">
+        <v>46225.407337962963</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1084"/>
+      <c r="F1084">
+        <v>2760314127</v>
+      </c>
+      <c r="G1084" s="2">
+        <v>1784724394114480</v>
+      </c>
+      <c r="H1084" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1084" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1084" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1084" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1084" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1084">
+        <v>19</v>
+      </c>
+      <c r="R1084" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S1084" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1085" s="1">
+        <v>46225.408113425925</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1085" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1085"/>
+      <c r="F1085">
+        <v>2766346163</v>
+      </c>
+      <c r="G1085" s="2">
+        <v>1784724461115750</v>
+      </c>
+      <c r="H1085" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1085" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1085" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1085" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1085" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1085">
+        <v>19</v>
+      </c>
+      <c r="R1085" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1085" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1086" s="1">
+        <v>46225.408263888887</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1086"/>
+      <c r="F1086">
+        <v>2766346176</v>
+      </c>
+      <c r="G1086" s="2">
+        <v>1784724474116000</v>
+      </c>
+      <c r="H1086" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1086" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1086" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1086" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1086" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1086" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1086">
+        <v>16</v>
+      </c>
+      <c r="R1086" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="S1086" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1087" s="1">
+        <v>46225.409074074072</v>
+      </c>
+      <c r="B1087" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1087"/>
+      <c r="F1087">
+        <v>2779134283</v>
+      </c>
+      <c r="G1087" s="2">
+        <v>1784724544117480</v>
+      </c>
+      <c r="H1087" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1087" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1087" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1087" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1087" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1087" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1087">
+        <v>16</v>
+      </c>
+      <c r="R1087" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1087" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1088" s="1">
+        <v>46225.40934027778</v>
+      </c>
+      <c r="B1088" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1088"/>
+      <c r="F1088">
+        <v>2779134306</v>
+      </c>
+      <c r="G1088" s="2">
+        <v>1784724567117860</v>
+      </c>
+      <c r="H1088" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1088" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1088" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1088" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1088" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1088" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1088">
+        <v>16</v>
+      </c>
+      <c r="R1088" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1088" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1089" s="1">
+        <v>46225.409618055557</v>
+      </c>
+      <c r="B1089" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1089"/>
+      <c r="F1089">
+        <v>2779134330</v>
+      </c>
+      <c r="G1089" s="2">
+        <v>1784724591118610</v>
+      </c>
+      <c r="H1089" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1089" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1089" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1089" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1089" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1089">
+        <v>19</v>
+      </c>
+      <c r="R1089" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1089" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1090" s="1">
+        <v>46225.410138888888</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1090"/>
+      <c r="F1090">
+        <v>2771994382</v>
+      </c>
+      <c r="G1090" s="2">
+        <v>1784724636119440</v>
+      </c>
+      <c r="H1090" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1090" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1090" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1090" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1090" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1090" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1090">
+        <v>16</v>
+      </c>
+      <c r="R1090" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="S1090" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1091" s="1">
+        <v>46225.410636574074</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1091"/>
+      <c r="F1091">
+        <v>2771994425</v>
+      </c>
+      <c r="G1091" s="2">
+        <v>1784724679120510</v>
+      </c>
+      <c r="H1091" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1091" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1091" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1091" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1091" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1091" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1091">
+        <v>16</v>
+      </c>
+      <c r="R1091" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="S1091" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1092" s="1">
+        <v>46225.411550925928</v>
+      </c>
+      <c r="B1092" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1092"/>
+      <c r="F1092">
+        <v>2749086489</v>
+      </c>
+      <c r="G1092" s="2">
+        <v>1784724758122620</v>
+      </c>
+      <c r="H1092" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1092" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1092" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1092" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1092" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1092" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1092">
+        <v>16</v>
+      </c>
+      <c r="R1092" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S1092" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1093" s="1">
+        <v>46225.411932870367</v>
+      </c>
+      <c r="B1093" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1093"/>
+      <c r="F1093">
+        <v>2749086522</v>
+      </c>
+      <c r="G1093" s="2">
+        <v>1784724791123130</v>
+      </c>
+      <c r="H1093" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1093" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1093" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1093" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1093" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1093" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1093">
+        <v>16</v>
+      </c>
+      <c r="R1093" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="S1093" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1094" s="1">
+        <v>46225.412638888891</v>
+      </c>
+      <c r="B1094" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1094"/>
+      <c r="F1094">
+        <v>2775472203</v>
+      </c>
+      <c r="G1094" s="2">
+        <v>1784724852124380</v>
+      </c>
+      <c r="H1094" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1094" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1094" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1094" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1094" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1094">
+        <v>19</v>
+      </c>
+      <c r="R1094" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1094" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1095" s="1">
+        <v>46225.412858796299</v>
+      </c>
+      <c r="B1095" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1095"/>
+      <c r="F1095">
+        <v>2775472222</v>
+      </c>
+      <c r="G1095" s="2">
+        <v>1784724871124730</v>
+      </c>
+      <c r="H1095" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1095" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1095" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1095" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1095" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1095" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1095">
+        <v>16</v>
+      </c>
+      <c r="R1095" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="S1095" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1096" s="1">
+        <v>46225.413831018515</v>
+      </c>
+      <c r="B1096" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1096"/>
+      <c r="F1096">
+        <v>2749398823</v>
+      </c>
+      <c r="G1096" s="2">
+        <v>1784724951126440</v>
+      </c>
+      <c r="H1096" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1096" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1096" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1096" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1096" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1096">
+        <v>17</v>
+      </c>
+      <c r="R1096" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1096" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1097" s="1">
+        <v>46225.414039351854</v>
+      </c>
+      <c r="B1097" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1097"/>
+      <c r="F1097">
+        <v>2749398841</v>
+      </c>
+      <c r="G1097" s="2">
+        <v>1784724969126850</v>
+      </c>
+      <c r="H1097" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1097" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1097" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1097" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1097" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1097">
+        <v>17</v>
+      </c>
+      <c r="R1097" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1097" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1098" s="1">
+        <v>46225.414212962962</v>
+      </c>
+      <c r="B1098" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1098"/>
+      <c r="F1098">
+        <v>2749398856</v>
+      </c>
+      <c r="G1098" s="2">
+        <v>1784724984127300</v>
+      </c>
+      <c r="H1098" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1098" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1098" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1098" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1098" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1098">
+        <v>17</v>
+      </c>
+      <c r="R1098" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1098" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1099" s="1">
+        <v>46225.414803240739</v>
+      </c>
+      <c r="B1099" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1099"/>
+      <c r="F1099">
+        <v>2781127404</v>
+      </c>
+      <c r="G1099" s="2">
+        <v>1784725039129170</v>
+      </c>
+      <c r="H1099" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1099" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1099" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1099" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1099" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1099" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1099">
+        <v>16</v>
+      </c>
+      <c r="R1099" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1099" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1100" s="1">
+        <v>46225.415208333332</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1100"/>
+      <c r="F1100">
+        <v>2781127439</v>
+      </c>
+      <c r="G1100" s="2">
+        <v>1784725074130100</v>
+      </c>
+      <c r="H1100" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1100" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1100" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1100" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1100" t="s">
+        <v>194</v>
+      </c>
+      <c r="N1100" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1100">
+        <v>16</v>
+      </c>
+      <c r="R1100" s="3">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="S1100" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1101" s="1">
+        <v>46225.416539351849</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1101"/>
+      <c r="F1101">
+        <v>2773264760</v>
+      </c>
+      <c r="G1101" s="2">
+        <v>1784725189132440</v>
+      </c>
+      <c r="H1101" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1101" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1101" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1101" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1101" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1101" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1101">
+        <v>16</v>
+      </c>
+      <c r="R1101" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S1101" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1102" s="1">
+        <v>46225.416956018518</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1102"/>
+      <c r="F1102">
+        <v>2773264796</v>
+      </c>
+      <c r="G1102" s="2">
+        <v>1784725225133640</v>
+      </c>
+      <c r="H1102" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1102" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1102" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1102" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1102" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1102" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1102">
+        <v>16</v>
+      </c>
+      <c r="R1102" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1102" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1103" s="1">
+        <v>46225.417233796295</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1103" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1103"/>
+      <c r="F1103">
+        <v>2773264820</v>
+      </c>
+      <c r="G1103" s="2">
+        <v>1784725249134270</v>
+      </c>
+      <c r="H1103" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1103" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1103" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1103" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1103" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1103">
+        <v>19</v>
+      </c>
+      <c r="R1103" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1103" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1104" s="1">
+        <v>46225.417696759258</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1104"/>
+      <c r="F1104">
+        <v>2775804913</v>
+      </c>
+      <c r="G1104" s="2">
+        <v>1784725289135090</v>
+      </c>
+      <c r="H1104" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1104" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1104" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1104" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1104" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1104" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1104">
+        <v>16</v>
+      </c>
+      <c r="R1104" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1104" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1105" s="1">
+        <v>46225.417870370373</v>
+      </c>
+      <c r="B1105" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1105" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1105"/>
+      <c r="F1105">
+        <v>2775804928</v>
+      </c>
+      <c r="G1105" s="2">
+        <v>1784725304135600</v>
+      </c>
+      <c r="H1105" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1105" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1105" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1105" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1105" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1105" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1105">
+        <v>16</v>
+      </c>
+      <c r="R1105" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1105" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1106" s="1">
+        <v>46225.41810185185</v>
+      </c>
+      <c r="B1106" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1106"/>
+      <c r="F1106">
+        <v>2775804948</v>
+      </c>
+      <c r="G1106" s="2">
+        <v>1784725324136270</v>
+      </c>
+      <c r="H1106" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1106" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1106" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1106" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1106" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1106" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1106">
+        <v>16</v>
+      </c>
+      <c r="R1106" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1106" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1107" s="1">
+        <v>46225.418611111112</v>
+      </c>
+      <c r="B1107" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1107" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1107"/>
+      <c r="F1107">
+        <v>2780572481</v>
+      </c>
+      <c r="G1107" s="2">
+        <v>1784725368137130</v>
+      </c>
+      <c r="H1107" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1107" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1107" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1107" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1107" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1107">
+        <v>19</v>
+      </c>
+      <c r="R1107" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S1107" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1108" s="1">
+        <v>46225.419027777774</v>
+      </c>
+      <c r="B1108" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1108" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1108"/>
+      <c r="F1108">
+        <v>2780572517</v>
+      </c>
+      <c r="G1108" s="2">
+        <v>1784725404137930</v>
+      </c>
+      <c r="H1108" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1108" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1108" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1108" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1108" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1108">
+        <v>19</v>
+      </c>
+      <c r="R1108" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1108" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1109" s="1">
+        <v>46225.419756944444</v>
+      </c>
+      <c r="B1109" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1109"/>
+      <c r="F1109">
+        <v>2748820040</v>
+      </c>
+      <c r="G1109" s="2">
+        <v>1784725467139850</v>
+      </c>
+      <c r="H1109" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1109" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1109" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1109" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1109" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1109">
+        <v>19</v>
+      </c>
+      <c r="R1109" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1109" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1110" s="1">
+        <v>46225.419872685183</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1110" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1110"/>
+      <c r="F1110">
+        <v>2748820049</v>
+      </c>
+      <c r="G1110" s="2">
+        <v>1784725477140090</v>
+      </c>
+      <c r="H1110" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1110" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1110" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1110" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1110" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1110">
+        <v>19</v>
+      </c>
+      <c r="R1110" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1110" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1111" s="1">
+        <v>46225.419976851852</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1111" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1111"/>
+      <c r="F1111">
+        <v>2748820058</v>
+      </c>
+      <c r="G1111" s="2">
+        <v>1784725486140330</v>
+      </c>
+      <c r="H1111" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1111" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1111" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1111" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1111" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1111">
+        <v>19</v>
+      </c>
+      <c r="R1111" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1111" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1112" s="1">
+        <v>46225.421041666668</v>
+      </c>
+      <c r="B1112" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1112" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1112"/>
+      <c r="F1112">
+        <v>2757408357</v>
+      </c>
+      <c r="G1112" s="2">
+        <v>1784725529141840</v>
+      </c>
+      <c r="H1112" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1112" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1112" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1112" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1112" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1112">
+        <v>19</v>
+      </c>
+      <c r="R1112" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1112" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1113" s="1">
+        <v>46225.421180555553</v>
+      </c>
+      <c r="B1113" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1113"/>
+      <c r="F1113">
+        <v>2757408418</v>
+      </c>
+      <c r="G1113" s="2">
+        <v>1784725590144150</v>
+      </c>
+      <c r="H1113" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1113" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1113" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1113" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1113" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1113" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1113">
+        <v>16</v>
+      </c>
+      <c r="R1113" s="3">
+        <v>1.4351851851851852E-3</v>
+      </c>
+      <c r="S1113" s="3">
+        <v>1.3541666666666667E-3</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1114" s="1">
+        <v>46225.424699074072</v>
+      </c>
+      <c r="B1114" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1114" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1114"/>
+      <c r="F1114">
+        <v>2784397837</v>
+      </c>
+      <c r="G1114" s="2">
+        <v>1784725894153280</v>
+      </c>
+      <c r="H1114" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1114" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1114" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1114" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1114" t="s">
+        <v>175</v>
+      </c>
+      <c r="N1114" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1114">
+        <v>16</v>
+      </c>
+      <c r="R1114" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1114" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1115" s="1">
+        <v>46225.425729166665</v>
+      </c>
+      <c r="B1115" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1115" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1115"/>
+      <c r="F1115">
+        <v>2784397926</v>
+      </c>
+      <c r="G1115" s="2">
+        <v>1784725983155680</v>
+      </c>
+      <c r="H1115" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1115" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1115" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1115" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1115" t="s">
+        <v>175</v>
+      </c>
+      <c r="N1115" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1115">
+        <v>16</v>
+      </c>
+      <c r="R1115" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="S1115" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1116" s="1">
+        <v>46225.426111111112</v>
+      </c>
+      <c r="B1116" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1116" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1116"/>
+      <c r="F1116">
+        <v>2784397959</v>
+      </c>
+      <c r="G1116" s="2">
+        <v>1784726016156390</v>
+      </c>
+      <c r="H1116" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1116" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1116" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1116" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1116" t="s">
+        <v>175</v>
+      </c>
+      <c r="N1116" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1116">
+        <v>16</v>
+      </c>
+      <c r="R1116" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+      <c r="S1116" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1117" s="1">
+        <v>46225.42659722222</v>
+      </c>
+      <c r="B1117" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1117" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1117"/>
+      <c r="F1117">
+        <v>2784398001</v>
+      </c>
+      <c r="G1117" s="2">
+        <v>1784726058157370</v>
+      </c>
+      <c r="H1117" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1117" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1117" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1117" t="s">
+        <v>222</v>
+      </c>
+      <c r="N1117" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1117">
+        <v>16</v>
+      </c>
+      <c r="R1117" s="3">
+        <v>0</v>
+      </c>
+      <c r="S1117" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1118" s="1">
+        <v>46225.426666666666</v>
+      </c>
+      <c r="B1118" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1118" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1118"/>
+      <c r="F1118">
+        <v>2784398007</v>
+      </c>
+      <c r="G1118" s="2">
+        <v>1784726064157590</v>
+      </c>
+      <c r="H1118" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1118" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1118" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1118" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1118" t="s">
+        <v>175</v>
+      </c>
+      <c r="N1118" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1118">
+        <v>16</v>
+      </c>
+      <c r="R1118" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="S1118" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1119" s="1">
+        <v>46225.427430555559</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1119"/>
+      <c r="F1119">
+        <v>2776849349</v>
+      </c>
+      <c r="G1119" s="2">
+        <v>1784726130159080</v>
+      </c>
+      <c r="H1119" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1119" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1119" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1119" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1119" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1119" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1119">
+        <v>16</v>
+      </c>
+      <c r="R1119" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1119" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1120" s="1">
+        <v>46225.42765046296</v>
+      </c>
+      <c r="B1120" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1120"/>
+      <c r="F1120">
+        <v>2776849367</v>
+      </c>
+      <c r="G1120" s="2">
+        <v>1784726149159440</v>
+      </c>
+      <c r="H1120" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1120" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1120" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1120" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1120" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1120" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1120">
+        <v>16</v>
+      </c>
+      <c r="R1120" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1120" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1121" s="1">
+        <v>46225.427893518521</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1121" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1121"/>
+      <c r="F1121">
+        <v>2776849388</v>
+      </c>
+      <c r="G1121" s="2">
+        <v>1784726170160260</v>
+      </c>
+      <c r="H1121" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1121" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1121" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1121" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1121" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1121" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1121">
+        <v>16</v>
+      </c>
+      <c r="R1121" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1121" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1122" s="1">
+        <v>46225.428599537037</v>
+      </c>
+      <c r="B1122" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1122" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1122"/>
+      <c r="F1122">
+        <v>2754730445</v>
+      </c>
+      <c r="G1122" s="2">
+        <v>1784726231161840</v>
+      </c>
+      <c r="H1122" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1122" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1122" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1122" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1122" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1122" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1122">
+        <v>16</v>
+      </c>
+      <c r="R1122" s="3">
+        <v>1.0532407407407407E-3</v>
+      </c>
+      <c r="S1122" s="3">
+        <v>9.9537037037037042E-4</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1123" s="1">
+        <v>46225.430451388886</v>
+      </c>
+      <c r="B1123" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1123" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1123"/>
+      <c r="F1123">
+        <v>1810052835</v>
+      </c>
+      <c r="G1123" s="2">
+        <v>1784726391166780</v>
+      </c>
+      <c r="H1123" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1123" t="s">
+        <v>213</v>
+      </c>
+      <c r="J1123" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1123" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1123" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1123">
+        <v>19</v>
+      </c>
+      <c r="R1123" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="S1123" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1124" s="1">
+        <v>46225.431562500002</v>
+      </c>
+      <c r="B1124" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1124" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1124"/>
+      <c r="F1124">
+        <v>1810052883</v>
+      </c>
+      <c r="G1124" s="2">
+        <v>1784726439168270</v>
+      </c>
+      <c r="H1124" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1124" t="s">
+        <v>213</v>
+      </c>
+      <c r="J1124" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1124" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1124" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1124">
+        <v>19</v>
+      </c>
+      <c r="R1124" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1124" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1125" s="1">
+        <v>46225.433518518519</v>
+      </c>
+      <c r="B1125" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1125"/>
+      <c r="F1125">
+        <v>1810053070</v>
+      </c>
+      <c r="G1125" s="2">
+        <v>1784726626173820</v>
+      </c>
+      <c r="H1125" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1125" t="s">
+        <v>213</v>
+      </c>
+      <c r="J1125" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1125" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1125" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1125">
+        <v>19</v>
+      </c>
+      <c r="R1125" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1125" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1126" s="1">
+        <v>46225.433715277781</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1126"/>
+      <c r="F1126">
+        <v>1809802133</v>
+      </c>
+      <c r="G1126" s="2">
+        <v>1784726673175310</v>
+      </c>
+      <c r="H1126" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1126" t="s">
+        <v>212</v>
+      </c>
+      <c r="J1126" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1126" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1126" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1126" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1126">
+        <v>16</v>
+      </c>
+      <c r="R1126" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1126" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1127" s="1">
+        <v>46225.43513888889</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1127" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1127"/>
+      <c r="F1127">
+        <v>1809901986</v>
+      </c>
+      <c r="G1127" s="2">
+        <v>1784726765177490</v>
+      </c>
+      <c r="H1127" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1127" t="s">
+        <v>215</v>
+      </c>
+      <c r="J1127" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1127" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1127" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1127">
+        <v>19</v>
+      </c>
+      <c r="R1127" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1127" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1128" s="1">
+        <v>46225.435567129629</v>
+      </c>
+      <c r="B1128" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1128" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1128"/>
+      <c r="F1128">
+        <v>1809902023</v>
+      </c>
+      <c r="G1128" s="2">
+        <v>1784726802178210</v>
+      </c>
+      <c r="H1128" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1128" t="s">
+        <v>215</v>
+      </c>
+      <c r="J1128" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1128" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1128" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1128">
+        <v>19</v>
+      </c>
+      <c r="R1128" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1128" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1129" s="1">
+        <v>46225.436435185184</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1129" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1129"/>
+      <c r="F1129">
+        <v>1817060424</v>
+      </c>
+      <c r="G1129" s="2">
+        <v>1784726903180870</v>
+      </c>
+      <c r="H1129" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1129" t="s">
+        <v>216</v>
+      </c>
+      <c r="J1129" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1129" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1129" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1129">
+        <v>19</v>
+      </c>
+      <c r="R1129" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1129" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1130" s="1">
+        <v>46225.436574074076</v>
+      </c>
+      <c r="B1130" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1130" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1130"/>
+      <c r="F1130">
+        <v>1817060436</v>
+      </c>
+      <c r="G1130" s="2">
+        <v>1784726915180980</v>
+      </c>
+      <c r="H1130" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1130" t="s">
+        <v>216</v>
+      </c>
+      <c r="J1130" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1130" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1130" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1130">
+        <v>19</v>
+      </c>
+      <c r="R1130" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1130" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1131" s="1">
+        <v>46225.437106481484</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1131" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1131"/>
+      <c r="F1131">
+        <v>2773624155</v>
+      </c>
+      <c r="G1131" s="2">
+        <v>1784726966182070</v>
+      </c>
+      <c r="H1131" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1131" t="s">
+        <v>218</v>
+      </c>
+      <c r="J1131" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1131" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1131" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1131">
+        <v>19</v>
+      </c>
+      <c r="R1131" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="S1131" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1132" s="1">
+        <v>46225.437199074076</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1132" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1132"/>
+      <c r="F1132">
+        <v>2773624163</v>
+      </c>
+      <c r="G1132" s="2">
+        <v>1784726974182260</v>
+      </c>
+      <c r="H1132" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1132" t="s">
+        <v>218</v>
+      </c>
+      <c r="J1132" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1132" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1132" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1132">
+        <v>19</v>
+      </c>
+      <c r="R1132" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="S1132" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1133" s="1">
+        <v>46225.442708333336</v>
+      </c>
+      <c r="B1133" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1133" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1133"/>
+      <c r="F1133">
+        <v>2781883225</v>
+      </c>
+      <c r="G1133" s="2">
+        <v>1784727450196080</v>
+      </c>
+      <c r="H1133" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1133" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1133" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1133" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1133" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1133" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1133">
+        <v>16</v>
+      </c>
+      <c r="R1133" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1133" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1134" s="1">
+        <v>46225.443124999998</v>
+      </c>
+      <c r="B1134" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1134" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1134"/>
+      <c r="F1134">
+        <v>2781883261</v>
+      </c>
+      <c r="G1134" s="2">
+        <v>1784727486197010</v>
+      </c>
+      <c r="H1134" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1134" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1134" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1134" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1134" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1134" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1134">
+        <v>16</v>
+      </c>
+      <c r="R1134" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="S1134" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1135" s="1">
+        <v>46225.443749999999</v>
+      </c>
+      <c r="B1135" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1135"/>
+      <c r="F1135">
+        <v>2781287491</v>
+      </c>
+      <c r="G1135" s="2">
+        <v>1784727540198630</v>
+      </c>
+      <c r="H1135" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1135" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1135" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1135" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1135" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1135">
+        <v>19</v>
+      </c>
+      <c r="R1135" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="S1135" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1136" s="1">
+        <v>46225.444027777776</v>
+      </c>
+      <c r="B1136" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1136"/>
+      <c r="F1136">
+        <v>2781287515</v>
+      </c>
+      <c r="G1136" s="2">
+        <v>1784727564199330</v>
+      </c>
+      <c r="H1136" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1136" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1136" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1136" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1136" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1136">
+        <v>19</v>
+      </c>
+      <c r="R1136" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1136" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1137" s="1">
+        <v>46225.444432870368</v>
+      </c>
+      <c r="B1137" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1137" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1137"/>
+      <c r="F1137">
+        <v>1820381030</v>
+      </c>
+      <c r="G1137" s="2">
+        <v>1784727593200060</v>
+      </c>
+      <c r="H1137" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1137" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1137" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1137" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1137" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1137">
+        <v>19</v>
+      </c>
+      <c r="R1137" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1137" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1138" s="1">
+        <v>46225.444571759261</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1138" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1138"/>
+      <c r="F1138">
+        <v>1820381043</v>
+      </c>
+      <c r="G1138" s="2">
+        <v>1784727606200390</v>
+      </c>
+      <c r="H1138" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1138" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1138" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1138" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1138" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1138">
+        <v>19</v>
+      </c>
+      <c r="R1138" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1138" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1139" s="1">
+        <v>46225.444722222222</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1139" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1139"/>
+      <c r="F1139">
+        <v>1820381055</v>
+      </c>
+      <c r="G1139" s="2">
+        <v>1784727618200640</v>
+      </c>
+      <c r="H1139" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1139" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1139" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1139" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1139" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1139">
+        <v>19</v>
+      </c>
+      <c r="R1139" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1139" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1140" s="1">
+        <v>46225.444884259261</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1140" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1140"/>
+      <c r="F1140">
+        <v>1820381070</v>
+      </c>
+      <c r="G1140" s="2">
+        <v>1784727633200820</v>
+      </c>
+      <c r="H1140" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1140" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1140" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1140" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1140" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1140">
+        <v>19</v>
+      </c>
+      <c r="R1140" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1140" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1141" s="1">
+        <v>46225.445416666669</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1141"/>
+      <c r="F1141">
+        <v>2757199201</v>
+      </c>
+      <c r="G1141" s="2">
+        <v>1784727684202000</v>
+      </c>
+      <c r="H1141" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1141" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1141" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1141" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1141" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1141">
+        <v>19</v>
+      </c>
+      <c r="R1141" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="S1141" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1142" s="1">
+        <v>46225.445775462962</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1142"/>
+      <c r="F1142">
+        <v>2757199232</v>
+      </c>
+      <c r="G1142" s="2">
+        <v>1784727715202420</v>
+      </c>
+      <c r="H1142" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1142" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1142" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1142" t="s">
+        <v>194</v>
+      </c>
+      <c r="N1142" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1142">
+        <v>16</v>
+      </c>
+      <c r="R1142" s="3">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="S1142" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1143" s="1">
+        <v>46225.446828703702</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1143"/>
+      <c r="F1143">
+        <v>2773541760</v>
+      </c>
+      <c r="G1143" s="2">
+        <v>1784727806204230</v>
+      </c>
+      <c r="H1143" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1143" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1143" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1143" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1143" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1143">
+        <v>19</v>
+      </c>
+      <c r="R1143" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1143" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1144" s="1">
+        <v>46225.446932870371</v>
+      </c>
+      <c r="B1144" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1144" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1144"/>
+      <c r="F1144">
+        <v>2773541770</v>
+      </c>
+      <c r="G1144" s="2">
+        <v>1784727815204480</v>
+      </c>
+      <c r="H1144" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1144" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1144" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1144" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1144" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1144">
+        <v>19</v>
+      </c>
+      <c r="R1144" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1144" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1145" s="1">
+        <v>46225.447071759256</v>
+      </c>
+      <c r="B1145" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1145" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1145"/>
+      <c r="F1145">
+        <v>2773541781</v>
+      </c>
+      <c r="G1145" s="2">
+        <v>1784727827204870</v>
+      </c>
+      <c r="H1145" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1145" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1145" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1145" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1145" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1145">
+        <v>19</v>
+      </c>
+      <c r="R1145" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1145" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1146" s="1">
+        <v>46225.44740740741</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1146"/>
+      <c r="F1146">
+        <v>2766369278</v>
+      </c>
+      <c r="G1146" s="2">
+        <v>1784727856205480</v>
+      </c>
+      <c r="H1146" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1146" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1146" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1146" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1146" t="s">
+        <v>132</v>
+      </c>
+      <c r="N1146" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1146">
+        <v>16</v>
+      </c>
+      <c r="R1146" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="S1146" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1147" s="1">
+        <v>46225.447858796295</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1147"/>
+      <c r="F1147">
+        <v>2766369317</v>
+      </c>
+      <c r="G1147" s="2">
+        <v>1784727895206610</v>
+      </c>
+      <c r="H1147" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1147" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1147" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1147" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1147" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1147" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1147">
+        <v>16</v>
+      </c>
+      <c r="R1147" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="S1147" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1148" s="1">
+        <v>46225.448773148149</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1148"/>
+      <c r="F1148">
+        <v>2773414377</v>
+      </c>
+      <c r="G1148" s="2">
+        <v>1784727974208490</v>
+      </c>
+      <c r="H1148" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1148" t="s">
+        <v>220</v>
+      </c>
+      <c r="J1148" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1148" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1148" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1148">
+        <v>19</v>
+      </c>
+      <c r="R1148" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1148" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1149" s="1">
+        <v>46225.448888888888</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1149"/>
+      <c r="F1149">
+        <v>2773414387</v>
+      </c>
+      <c r="G1149" s="2">
+        <v>1784727984208700</v>
+      </c>
+      <c r="H1149" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1149" t="s">
+        <v>220</v>
+      </c>
+      <c r="J1149" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1149" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1149" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1149">
+        <v>19</v>
+      </c>
+      <c r="R1149" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1149" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1150" s="1">
+        <v>46225.44935185185</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1150"/>
+      <c r="F1150">
+        <v>2765970915</v>
+      </c>
+      <c r="G1150" s="2">
+        <v>1784728024209930</v>
+      </c>
+      <c r="H1150" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1150" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1150" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1150" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1150" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1150">
+        <v>19</v>
+      </c>
+      <c r="R1150" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1150" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1151" s="1">
+        <v>46225.449479166666</v>
+      </c>
+      <c r="B1151" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1151"/>
+      <c r="F1151">
+        <v>2765970926</v>
+      </c>
+      <c r="G1151" s="2">
+        <v>1784728035210250</v>
+      </c>
+      <c r="H1151" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1151" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1151" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1151" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1151" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1151">
+        <v>19</v>
+      </c>
+      <c r="R1151" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="S1151" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1152" s="1">
+        <v>46225.449548611112</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1152"/>
+      <c r="F1152">
+        <v>2765970932</v>
+      </c>
+      <c r="G1152" s="2">
+        <v>1784728041210390</v>
+      </c>
+      <c r="H1152" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1152" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1152" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1152" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1152" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1152">
+        <v>19</v>
+      </c>
+      <c r="R1152" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="S1152" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1153" s="1">
+        <v>46225.450069444443</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1153"/>
+      <c r="F1153">
+        <v>2783447087</v>
+      </c>
+      <c r="G1153" s="2">
+        <v>1784728085211700</v>
+      </c>
+      <c r="H1153" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1153" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1153" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1153" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1153" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1153" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1153">
+        <v>16</v>
+      </c>
+      <c r="R1153" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="S1153" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1154" s="1">
+        <v>46225.450682870367</v>
+      </c>
+      <c r="B1154" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1154"/>
+      <c r="F1154">
+        <v>2783447140</v>
+      </c>
+      <c r="G1154" s="2">
+        <v>1784728139213180</v>
+      </c>
+      <c r="H1154" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1154" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1154" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1154" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1154" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1154" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1154">
+        <v>16</v>
+      </c>
+      <c r="R1154" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1154" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1155" s="1">
+        <v>46225.450995370367</v>
+      </c>
+      <c r="B1155" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1155"/>
+      <c r="F1155">
+        <v>2783447167</v>
+      </c>
+      <c r="G1155" s="2">
+        <v>1784728166213820</v>
+      </c>
+      <c r="H1155" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1155" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1155" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1155" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1155" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1155">
+        <v>19</v>
+      </c>
+      <c r="R1155" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1155" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1156" s="1">
+        <v>46225.459224537037</v>
+      </c>
+      <c r="B1156" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1156"/>
+      <c r="F1156">
+        <v>2775781659</v>
+      </c>
+      <c r="G1156" s="2">
+        <v>1784728877237380</v>
+      </c>
+      <c r="H1156" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1156" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1156" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1156" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1156" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1156">
+        <v>19</v>
+      </c>
+      <c r="R1156" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="S1156" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1157" s="1">
+        <v>46225.460081018522</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1157"/>
+      <c r="F1157">
+        <v>2766467970</v>
+      </c>
+      <c r="G1157" s="2">
+        <v>1784728951239620</v>
+      </c>
+      <c r="H1157" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1157" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1157" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1157" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1157" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1157">
+        <v>19</v>
+      </c>
+      <c r="R1157" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1157" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1158" s="1">
+        <v>46225.460243055553</v>
+      </c>
+      <c r="B1158" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1158"/>
+      <c r="F1158">
+        <v>2766467984</v>
+      </c>
+      <c r="G1158" s="2">
+        <v>1784728965240150</v>
+      </c>
+      <c r="H1158" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1158" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1158" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1158" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1158" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1158">
+        <v>19</v>
+      </c>
+      <c r="R1158" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="S1158" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1159" s="1">
+        <v>46225.461018518516</v>
+      </c>
+      <c r="B1159" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1159"/>
+      <c r="F1159">
+        <v>2749379480</v>
+      </c>
+      <c r="G1159" s="2">
+        <v>1784729032242380</v>
+      </c>
+      <c r="H1159" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1159" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1159" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1159" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1159" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1159">
+        <v>19</v>
+      </c>
+      <c r="R1159" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1159" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1160" s="1">
+        <v>46225.461516203701</v>
+      </c>
+      <c r="B1160" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1160" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1160"/>
+      <c r="F1160">
+        <v>2784643524</v>
+      </c>
+      <c r="G1160" s="2">
+        <v>1784729075243740</v>
+      </c>
+      <c r="H1160" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1160" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1160" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1160" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1160" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1160" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1160">
+        <v>16</v>
+      </c>
+      <c r="R1160" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="S1160" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1161" s="1">
+        <v>46225.462164351855</v>
+      </c>
+      <c r="B1161" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1161"/>
+      <c r="F1161">
+        <v>2777050707</v>
+      </c>
+      <c r="G1161" s="2">
+        <v>1784729131245750</v>
+      </c>
+      <c r="H1161" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1161" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1161" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1161" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1161" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1161">
+        <v>19</v>
+      </c>
+      <c r="R1161" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="S1161" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1162" s="1">
+        <v>46225.462476851855</v>
+      </c>
+      <c r="B1162" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1162"/>
+      <c r="F1162">
+        <v>2777050734</v>
+      </c>
+      <c r="G1162" s="2">
+        <v>1784729158246440</v>
+      </c>
+      <c r="H1162" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1162" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1162" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1162" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1162" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1162">
+        <v>19</v>
+      </c>
+      <c r="R1162" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1162" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1163" s="1">
+        <v>46225.46329861111</v>
+      </c>
+      <c r="B1163" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1163"/>
+      <c r="F1163">
+        <v>2766112140</v>
+      </c>
+      <c r="G1163" s="2">
+        <v>1784729212247780</v>
+      </c>
+      <c r="H1163" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1163" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1163" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1163" t="s">
+        <v>222</v>
+      </c>
+      <c r="N1163" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1163">
+        <v>34</v>
+      </c>
+      <c r="R1163" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1163" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1164" s="1">
+        <v>46225.463460648149</v>
+      </c>
+      <c r="B1164" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1164"/>
+      <c r="F1164">
+        <v>2766112171</v>
+      </c>
+      <c r="G1164" s="2">
+        <v>1784729243248330</v>
+      </c>
+      <c r="H1164" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1164" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1164" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1164" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1164" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1164">
+        <v>1</v>
+      </c>
+      <c r="R1164" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1164" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1165" s="1">
+        <v>46225.463599537034</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1165"/>
+      <c r="F1165">
+        <v>2766112183</v>
+      </c>
+      <c r="G1165" s="2">
+        <v>1784729255248530</v>
+      </c>
+      <c r="H1165" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1165" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1165" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1165" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1165" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1165">
+        <v>1</v>
+      </c>
+      <c r="R1165" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1165" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1166" s="1">
+        <v>46225.463842592595</v>
+      </c>
+      <c r="B1166" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1166" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1166"/>
+      <c r="F1166">
+        <v>2780307288</v>
+      </c>
+      <c r="G1166" s="2">
+        <v>1784729276249440</v>
+      </c>
+      <c r="H1166" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1166" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1166" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1166" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1166" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1166">
+        <v>19</v>
+      </c>
+      <c r="R1166" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1166" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1167" s="1">
+        <v>46225.46398148148</v>
+      </c>
+      <c r="B1167" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1167" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1167"/>
+      <c r="F1167">
+        <v>2780307299</v>
+      </c>
+      <c r="G1167" s="2">
+        <v>1784729288249630</v>
+      </c>
+      <c r="H1167" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1167" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1167" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1167" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1167" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1167">
+        <v>19</v>
+      </c>
+      <c r="R1167" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1167" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1168" s="1">
+        <v>46225.464409722219</v>
+      </c>
+      <c r="B1168" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1168"/>
+      <c r="F1168">
+        <v>2749163307</v>
+      </c>
+      <c r="G1168" s="2">
+        <v>1784729325250820</v>
+      </c>
+      <c r="H1168" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1168" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1168" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1168" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1168" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1168" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1168">
+        <v>16</v>
+      </c>
+      <c r="R1168" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S1168" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1169" s="1">
+        <v>46225.464918981481</v>
+      </c>
+      <c r="B1169" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1169" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1169"/>
+      <c r="F1169">
+        <v>2749163351</v>
+      </c>
+      <c r="G1169" s="2">
+        <v>1784729369252350</v>
+      </c>
+      <c r="H1169" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1169" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1169" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1169" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1169" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1169" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1169">
+        <v>16</v>
+      </c>
+      <c r="R1169" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1169" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1170" s="1">
+        <v>46225.46638888889</v>
+      </c>
+      <c r="B1170" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1170"/>
+      <c r="F1170">
+        <v>2749163478</v>
+      </c>
+      <c r="G1170" s="2">
+        <v>1784729496255600</v>
+      </c>
+      <c r="H1170" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1170" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1170" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1170" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1170" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1170" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1170">
+        <v>16</v>
+      </c>
+      <c r="R1170" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1170" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1171" s="1">
+        <v>46225.466736111113</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1171" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1171"/>
+      <c r="F1171">
+        <v>2782684704</v>
+      </c>
+      <c r="G1171" s="2">
+        <v>1784729526256550</v>
+      </c>
+      <c r="H1171" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1171" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1171" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1171" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1171" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1171" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1171">
+        <v>16</v>
+      </c>
+      <c r="R1171" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1171" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1172" s="1">
+        <v>46225.466967592591</v>
+      </c>
+      <c r="B1172" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1172" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1172"/>
+      <c r="F1172">
+        <v>2782684724</v>
+      </c>
+      <c r="G1172" s="2">
+        <v>1784729546256960</v>
+      </c>
+      <c r="H1172" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1172" t="s">
+        <v>102</v>
+      </c>
+      <c r="J1172" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1172" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1172" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1172" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1172">
+        <v>16</v>
+      </c>
+      <c r="R1172" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1172" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1173" s="1">
+        <v>46225.467372685183</v>
+      </c>
+      <c r="B1173" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1173" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1173"/>
+      <c r="F1173">
+        <v>2762109391</v>
+      </c>
+      <c r="G1173" s="2">
+        <v>1784729581258070</v>
+      </c>
+      <c r="H1173" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1173" t="s">
+        <v>103</v>
+      </c>
+      <c r="J1173" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1173" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1173" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1173">
+        <v>19</v>
+      </c>
+      <c r="R1173" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="S1173" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1174" s="1">
+        <v>46225.467488425929</v>
+      </c>
+      <c r="B1174" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1174" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1174"/>
+      <c r="F1174">
+        <v>2762109401</v>
+      </c>
+      <c r="G1174" s="2">
+        <v>1784729591258530</v>
+      </c>
+      <c r="H1174" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1174" t="s">
+        <v>103</v>
+      </c>
+      <c r="J1174" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1174" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1174" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1174">
+        <v>19</v>
+      </c>
+      <c r="R1174" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1174" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1175" s="1">
+        <v>46225.467847222222</v>
+      </c>
+      <c r="B1175" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1175" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1175"/>
+      <c r="F1175">
+        <v>2777641843</v>
+      </c>
+      <c r="G1175" s="2">
+        <v>1784729622259740</v>
+      </c>
+      <c r="H1175" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1175" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1175" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1175" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1175" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1175">
+        <v>19</v>
+      </c>
+      <c r="R1175" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="S1175" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1176" s="1">
+        <v>46225.468541666669</v>
+      </c>
+      <c r="B1176" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1176" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1176"/>
+      <c r="F1176">
+        <v>2774879363</v>
+      </c>
+      <c r="G1176" s="2">
+        <v>1784729682262150</v>
+      </c>
+      <c r="H1176" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1176" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1176" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1176" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1176" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1176" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1176">
+        <v>16</v>
+      </c>
+      <c r="R1176" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="S1176" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1177" s="1">
+        <v>46225.468819444446</v>
+      </c>
+      <c r="B1177" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1177"/>
+      <c r="F1177">
+        <v>2774879388</v>
+      </c>
+      <c r="G1177" s="2">
+        <v>1784729706263070</v>
+      </c>
+      <c r="H1177" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1177" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1177" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1177" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1177" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1177">
+        <v>19</v>
+      </c>
+      <c r="R1177" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1177" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1178" s="1">
+        <v>46225.47078703704</v>
+      </c>
+      <c r="B1178" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1178"/>
+      <c r="F1178">
+        <v>2749464070</v>
+      </c>
+      <c r="G1178" s="2">
+        <v>1784729876268380</v>
+      </c>
+      <c r="H1178" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1178" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1178" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1178" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1178" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1178">
+        <v>19</v>
+      </c>
+      <c r="R1178" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1178" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1179" s="1">
+        <v>46225.470949074072</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1179" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1179"/>
+      <c r="F1179">
+        <v>2749464084</v>
+      </c>
+      <c r="G1179" s="2">
+        <v>1784729890268760</v>
+      </c>
+      <c r="H1179" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1179" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1179" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1179" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1179" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1179">
+        <v>19</v>
+      </c>
+      <c r="R1179" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1179" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1180" s="1">
+        <v>46225.471238425926</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1180" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1180"/>
+      <c r="F1180">
+        <v>2775553067</v>
+      </c>
+      <c r="G1180" s="2">
+        <v>1784729915269520</v>
+      </c>
+      <c r="H1180" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1180" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1180" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1180" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1180" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1180" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1180">
+        <v>16</v>
+      </c>
+      <c r="R1180" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1180" s="3">
+        <v>1.9675925925925926E-4</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1181" s="1">
+        <v>46225.471666666665</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1181" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1181"/>
+      <c r="F1181">
+        <v>2775553104</v>
+      </c>
+      <c r="G1181" s="2">
+        <v>1784729952270790</v>
+      </c>
+      <c r="H1181" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1181" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1181" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1181" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1181" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1181" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1181">
+        <v>16</v>
+      </c>
+      <c r="R1181" s="3">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="S1181" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1182" s="1">
+        <v>46225.472581018519</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1182" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1182"/>
+      <c r="F1182">
+        <v>2757784484</v>
+      </c>
+      <c r="G1182" s="2">
+        <v>1784730031272410</v>
+      </c>
+      <c r="H1182" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1182" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1182" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1182" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1182" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1182">
+        <v>19</v>
+      </c>
+      <c r="R1182" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="S1182" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1183" s="1">
+        <v>46225.473113425927</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1183" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1183"/>
+      <c r="F1183">
+        <v>2757784530</v>
+      </c>
+      <c r="G1183" s="2">
+        <v>1784730077273810</v>
+      </c>
+      <c r="H1183" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1183" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1183" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1183" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1183" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1183">
+        <v>19</v>
+      </c>
+      <c r="R1183" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S1183" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1184" s="1">
+        <v>46225.473773148151</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1184" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1184"/>
+      <c r="F1184">
+        <v>2765976414</v>
+      </c>
+      <c r="G1184" s="2">
+        <v>1784730134275420</v>
+      </c>
+      <c r="H1184" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1184" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1184" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1184" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1184" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1184">
+        <v>19</v>
+      </c>
+      <c r="R1184" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S1184" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1185" s="1">
+        <v>46225.474444444444</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1185" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1185"/>
+      <c r="F1185">
+        <v>2772530219</v>
+      </c>
+      <c r="G1185" s="2">
+        <v>1784730192276780</v>
+      </c>
+      <c r="H1185" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1185" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1185" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1185" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1185" t="s">
+        <v>175</v>
+      </c>
+      <c r="N1185" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1185">
+        <v>16</v>
+      </c>
+      <c r="R1185" s="3">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="S1185" s="3">
+        <v>1.0416666666666667E-3</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1186" s="1">
+        <v>46225.475775462961</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1186"/>
+      <c r="F1186">
+        <v>2772530334</v>
+      </c>
+      <c r="G1186" s="2">
+        <v>1784730307280070</v>
+      </c>
+      <c r="H1186" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1186" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1186" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1186" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1186" t="s">
+        <v>132</v>
+      </c>
+      <c r="N1186" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1186">
+        <v>16</v>
+      </c>
+      <c r="R1186" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1186" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1187" s="1">
+        <v>46225.476238425923</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1187"/>
+      <c r="F1187">
+        <v>2772530374</v>
+      </c>
+      <c r="G1187" s="2">
+        <v>1784730347281310</v>
+      </c>
+      <c r="H1187" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1187" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1187" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1187" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1187" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1187">
+        <v>19</v>
+      </c>
+      <c r="R1187" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="S1187" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1188" s="1">
+        <v>46225.477314814816</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1188" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1188"/>
+      <c r="F1188">
+        <v>2752477915</v>
+      </c>
+      <c r="G1188" s="2">
+        <v>1784730440283050</v>
+      </c>
+      <c r="H1188" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1188" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1188" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1188" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1188" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1188">
+        <v>19</v>
+      </c>
+      <c r="R1188" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1188" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1189" s="1">
+        <v>46225.477488425924</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1189" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1189"/>
+      <c r="F1189">
+        <v>2752477930</v>
+      </c>
+      <c r="G1189" s="2">
+        <v>1784730455283490</v>
+      </c>
+      <c r="H1189" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1189" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1189" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1189" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1189" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1189">
+        <v>19</v>
+      </c>
+      <c r="R1189" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1189" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1190" s="1">
+        <v>46225.478148148148</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1190" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1190"/>
+      <c r="F1190">
+        <v>2778935139</v>
+      </c>
+      <c r="G1190" s="2">
+        <v>1784730512284890</v>
+      </c>
+      <c r="H1190" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1190" t="s">
+        <v>115</v>
+      </c>
+      <c r="J1190" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1190" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1190" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1190">
+        <v>19</v>
+      </c>
+      <c r="R1190" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="S1190" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1191" s="1">
+        <v>46225.479421296295</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1191" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1191"/>
+      <c r="F1191">
+        <v>2748882866</v>
+      </c>
+      <c r="G1191" s="2">
+        <v>1784730622288170</v>
+      </c>
+      <c r="H1191" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1191" t="s">
+        <v>116</v>
+      </c>
+      <c r="J1191" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1191" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1191" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1191">
+        <v>16</v>
+      </c>
+      <c r="R1191" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S1191" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1192" s="1">
+        <v>46225.48028935185</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1192" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1192"/>
+      <c r="F1192">
+        <v>2749919334</v>
+      </c>
+      <c r="G1192" s="2">
+        <v>1784730697290200</v>
+      </c>
+      <c r="H1192" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1192" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1192" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1192" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1192" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1192" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1192">
+        <v>16</v>
+      </c>
+      <c r="R1192" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S1192" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1193" s="1">
+        <v>46225.481041666666</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1193" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1193"/>
+      <c r="F1193">
+        <v>2753630153</v>
+      </c>
+      <c r="G1193" s="2">
+        <v>1784730762291960</v>
+      </c>
+      <c r="H1193" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1193" t="s">
+        <v>118</v>
+      </c>
+      <c r="J1193" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1193" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1193" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1193" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1193">
+        <v>16</v>
+      </c>
+      <c r="R1193" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+      <c r="S1193" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1194" s="1">
+        <v>46225.481562499997</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1194" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1194"/>
+      <c r="F1194">
+        <v>2757920338</v>
+      </c>
+      <c r="G1194" s="2">
+        <v>1784730807292730</v>
+      </c>
+      <c r="H1194" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1194" t="s">
+        <v>120</v>
+      </c>
+      <c r="J1194" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1194" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1194" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1194">
+        <v>19</v>
+      </c>
+      <c r="R1194" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S1194" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1195" s="1">
+        <v>46225.482222222221</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1195"/>
+      <c r="F1195">
+        <v>2766888198</v>
+      </c>
+      <c r="G1195" s="2">
+        <v>1784730864294190</v>
+      </c>
+      <c r="H1195" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1195" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1195" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1195" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1195" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1195">
+        <v>19</v>
+      </c>
+      <c r="R1195" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+      <c r="S1195" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1196" s="1">
+        <v>46225.482893518521</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1196" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1196"/>
+      <c r="F1196">
+        <v>2757885813</v>
+      </c>
+      <c r="G1196" s="2">
+        <v>1784730922295610</v>
+      </c>
+      <c r="H1196" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1196" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1196" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1196" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1196" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1196">
+        <v>16</v>
+      </c>
+      <c r="R1196" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="S1196" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1197" s="1">
+        <v>46225.48296296296</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1197"/>
+      <c r="F1197">
+        <v>2757885819</v>
+      </c>
+      <c r="G1197" s="2">
+        <v>1784730928295740</v>
+      </c>
+      <c r="H1197" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1197" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1197" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1197" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1197" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1197">
+        <v>19</v>
+      </c>
+      <c r="R1197" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1197" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1198" s="1">
+        <v>46225.483217592591</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1198"/>
+      <c r="F1198">
+        <v>2783183245</v>
+      </c>
+      <c r="G1198" s="2">
+        <v>1784730950296380</v>
+      </c>
+      <c r="H1198" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1198" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1198" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1198" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1198" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1198">
+        <v>19</v>
+      </c>
+      <c r="R1198" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="S1198" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1199" s="1">
+        <v>46225.483738425923</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1199" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1199"/>
+      <c r="F1199">
+        <v>2782995016</v>
+      </c>
+      <c r="G1199" s="2">
+        <v>1784730995297460</v>
+      </c>
+      <c r="H1199" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1199" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1199" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1199" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1199" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1199">
+        <v>19</v>
+      </c>
+      <c r="R1199" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1199" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1200" s="1">
+        <v>46225.483946759261</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1200"/>
+      <c r="F1200">
+        <v>2782995034</v>
+      </c>
+      <c r="G1200" s="2">
+        <v>1784731013297860</v>
+      </c>
+      <c r="H1200" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1200" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1200" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1200" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1200" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1200" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1200">
+        <v>16</v>
+      </c>
+      <c r="R1200" s="3">
+        <v>2.2222222222222222E-3</v>
+      </c>
+      <c r="S1200" s="3">
+        <v>2.1527777777777778E-3</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1201" s="1">
+        <v>46225.487546296295</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1201"/>
+      <c r="F1201">
+        <v>2768754983</v>
+      </c>
+      <c r="G1201" s="2">
+        <v>1784731324307980</v>
+      </c>
+      <c r="H1201" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1201" t="s">
+        <v>128</v>
+      </c>
+      <c r="J1201" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1201" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1201" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1201" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1201">
+        <v>16</v>
+      </c>
+      <c r="R1201" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1201" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1202" s="1">
+        <v>46225.487881944442</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1202"/>
+      <c r="F1202">
+        <v>2768755012</v>
+      </c>
+      <c r="G1202" s="2">
+        <v>1784731353308780</v>
+      </c>
+      <c r="H1202" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1202" t="s">
+        <v>128</v>
+      </c>
+      <c r="J1202" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1202" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1202" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1202">
+        <v>19</v>
+      </c>
+      <c r="R1202" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="S1202" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1203" s="1">
+        <v>46225.488541666666</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1203"/>
+      <c r="F1203">
+        <v>2766266663</v>
+      </c>
+      <c r="G1203" s="2">
+        <v>1784731410310490</v>
+      </c>
+      <c r="H1203" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1203" t="s">
+        <v>129</v>
+      </c>
+      <c r="J1203" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1203" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1203" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1203">
+        <v>19</v>
+      </c>
+      <c r="R1203" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S1203" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1204" s="1">
+        <v>46225.488865740743</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1204"/>
+      <c r="F1204">
+        <v>2766266691</v>
+      </c>
+      <c r="G1204" s="2">
+        <v>1784731438311380</v>
+      </c>
+      <c r="H1204" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1204" t="s">
+        <v>129</v>
+      </c>
+      <c r="J1204" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1204" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1204" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1204">
+        <v>19</v>
+      </c>
+      <c r="R1204" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1204" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1205" s="1">
+        <v>46225.489189814813</v>
+      </c>
+      <c r="B1205" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1205"/>
+      <c r="F1205">
+        <v>2759663742</v>
+      </c>
+      <c r="G1205" s="2">
+        <v>1784731466312190</v>
+      </c>
+      <c r="H1205" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1205" t="s">
+        <v>130</v>
+      </c>
+      <c r="J1205" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1205" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1205" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1205" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1205">
+        <v>16</v>
+      </c>
+      <c r="R1205" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="S1205" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1206" s="1">
+        <v>46225.489687499998</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1206"/>
+      <c r="F1206">
+        <v>2782341925</v>
+      </c>
+      <c r="G1206" s="2">
+        <v>1784731509313340</v>
+      </c>
+      <c r="H1206" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1206" t="s">
+        <v>133</v>
+      </c>
+      <c r="J1206" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1206" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1206" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1206" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1206">
+        <v>16</v>
+      </c>
+      <c r="R1206" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="S1206" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1207" s="1">
+        <v>46225.490578703706</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1207"/>
+      <c r="F1207">
+        <v>2783741712</v>
+      </c>
+      <c r="G1207" s="2">
+        <v>1784731586315690</v>
+      </c>
+      <c r="H1207" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1207" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1207" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1207" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1207" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1207">
+        <v>19</v>
+      </c>
+      <c r="R1207" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="S1207" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1208" s="1">
+        <v>46225.491122685184</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1208"/>
+      <c r="F1208">
+        <v>2784020580</v>
+      </c>
+      <c r="G1208" s="2">
+        <v>1784731633316830</v>
+      </c>
+      <c r="H1208" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1208" t="s">
+        <v>136</v>
+      </c>
+      <c r="J1208" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1208" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1208" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1208">
+        <v>19</v>
+      </c>
+      <c r="R1208" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="S1208" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1209" s="1">
+        <v>46225.491342592592</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1209"/>
+      <c r="F1209">
+        <v>2784020599</v>
+      </c>
+      <c r="G1209" s="2">
+        <v>1784731652317530</v>
+      </c>
+      <c r="H1209" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1209" t="s">
+        <v>136</v>
+      </c>
+      <c r="J1209" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1209" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1209" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1209" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1209">
+        <v>16</v>
+      </c>
+      <c r="R1209" s="3">
+        <v>1.0416666666666667E-3</v>
+      </c>
+      <c r="S1209" s="3">
+        <v>9.7222222222222219E-4</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1210" s="1">
+        <v>46225.493263888886</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1210"/>
+      <c r="F1210">
+        <v>2781576294</v>
+      </c>
+      <c r="G1210" s="2">
+        <v>1784731818321670</v>
+      </c>
+      <c r="H1210" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1210" t="s">
+        <v>137</v>
+      </c>
+      <c r="J1210" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1210" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1210" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1210" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1210">
+        <v>16</v>
+      </c>
+      <c r="R1210" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1210" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1211" s="1">
+        <v>46225.493483796294</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1211"/>
+      <c r="F1211">
+        <v>2781576313</v>
+      </c>
+      <c r="G1211" s="2">
+        <v>1784731837322280</v>
+      </c>
+      <c r="H1211" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1211" t="s">
+        <v>137</v>
+      </c>
+      <c r="J1211" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1211" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1211" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1211" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1211">
+        <v>16</v>
+      </c>
+      <c r="R1211" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1211" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1212" s="1">
+        <v>46225.493831018517</v>
+      </c>
+      <c r="B1212" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1212"/>
+      <c r="F1212">
+        <v>2780875662</v>
+      </c>
+      <c r="G1212" s="2">
+        <v>1784731867322920</v>
+      </c>
+      <c r="H1212" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1212" t="s">
+        <v>138</v>
+      </c>
+      <c r="J1212" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1212" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1212" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1212" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1212">
+        <v>16</v>
+      </c>
+      <c r="R1212" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="S1212" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1213" s="1">
+        <v>46225.494675925926</v>
+      </c>
+      <c r="B1213" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1213"/>
+      <c r="F1213">
+        <v>2781775856</v>
+      </c>
+      <c r="G1213" s="2">
+        <v>1784731940325140</v>
+      </c>
+      <c r="H1213" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1213" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1213" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1213" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1213" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1213" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1213">
+        <v>16</v>
+      </c>
+      <c r="R1213" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="S1213" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1214" s="1">
+        <v>46225.495046296295</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1214"/>
+      <c r="F1214">
+        <v>2781775888</v>
+      </c>
+      <c r="G1214" s="2">
+        <v>1784731972326230</v>
+      </c>
+      <c r="H1214" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1214" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1214" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1214" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1214" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1214" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1214">
+        <v>16</v>
+      </c>
+      <c r="R1214" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1214" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1215" s="1">
+        <v>46225.495578703703</v>
+      </c>
+      <c r="B1215" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1215"/>
+      <c r="F1215">
+        <v>2774687509</v>
+      </c>
+      <c r="G1215" s="2">
+        <v>1784732018327360</v>
+      </c>
+      <c r="H1215" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1215" t="s">
+        <v>140</v>
+      </c>
+      <c r="J1215" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1215" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1215" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1215">
+        <v>19</v>
+      </c>
+      <c r="R1215" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="S1215" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1216" s="1">
+        <v>46225.496516203704</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1216"/>
+      <c r="F1216">
+        <v>2776724504</v>
+      </c>
+      <c r="G1216" s="2">
+        <v>1784732099328620</v>
+      </c>
+      <c r="H1216" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1216" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1216" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1216" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1216" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1216">
+        <v>19</v>
+      </c>
+      <c r="R1216" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1216" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1217" s="1">
+        <v>46225.496736111112</v>
+      </c>
+      <c r="B1217" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1217"/>
+      <c r="F1217">
+        <v>2776724523</v>
+      </c>
+      <c r="G1217" s="2">
+        <v>1784732118328910</v>
+      </c>
+      <c r="H1217" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1217" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1217" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1217" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1217" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1217">
+        <v>19</v>
+      </c>
+      <c r="R1217" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1217" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1218" s="1">
+        <v>46225.497534722221</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1218"/>
+      <c r="F1218">
+        <v>2784104831</v>
+      </c>
+      <c r="G1218" s="2">
+        <v>1784732187329820</v>
+      </c>
+      <c r="H1218" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1218" t="s">
+        <v>142</v>
+      </c>
+      <c r="J1218" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1218" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1218" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1218" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1218">
+        <v>16</v>
+      </c>
+      <c r="R1218" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+      <c r="S1218" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1219" s="1">
+        <v>46225.498148148145</v>
+      </c>
+      <c r="B1219" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1219"/>
+      <c r="F1219">
+        <v>2757904864</v>
+      </c>
+      <c r="G1219" s="2">
+        <v>1784732240331050</v>
+      </c>
+      <c r="H1219" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1219" t="s">
+        <v>145</v>
+      </c>
+      <c r="J1219" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1219" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1219" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1219" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1219">
+        <v>16</v>
+      </c>
+      <c r="R1219" s="3">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="S1219" s="3">
+        <v>1.5393518518518519E-3</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1220" s="1">
+        <v>46225.505636574075</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1220"/>
+      <c r="F1220">
+        <v>2753167804</v>
+      </c>
+      <c r="G1220" s="2">
+        <v>1784732887343510</v>
+      </c>
+      <c r="H1220" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1220" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1220" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1220" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1220" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1220" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1220">
+        <v>16</v>
+      </c>
+      <c r="R1220" s="3">
+        <v>2.0138888888888888E-3</v>
+      </c>
+      <c r="S1220" s="3">
+        <v>1.8634259259259259E-3</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1221" s="1">
+        <v>46225.508761574078</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1221"/>
+      <c r="F1221">
+        <v>2782653770</v>
+      </c>
+      <c r="G1221" s="2">
+        <v>1784733157350700</v>
+      </c>
+      <c r="H1221" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1221" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1221" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1221" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1221" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1221">
+        <v>19</v>
+      </c>
+      <c r="R1221" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="S1221" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1222" s="1">
+        <v>46225.510196759256</v>
+      </c>
+      <c r="B1222" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1222"/>
+      <c r="F1222">
+        <v>2757204747</v>
+      </c>
+      <c r="G1222" s="2">
+        <v>1784733230351660</v>
+      </c>
+      <c r="H1222" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1222" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1222" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1222" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1222" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1222">
+        <v>19</v>
+      </c>
+      <c r="R1222" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1222" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1223" s="1">
+        <v>46225.510844907411</v>
+      </c>
+      <c r="B1223" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1223"/>
+      <c r="F1223">
+        <v>2782653950</v>
+      </c>
+      <c r="G1223" s="2">
+        <v>1784733337354080</v>
+      </c>
+      <c r="H1223" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1223" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1223" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1223" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1223" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1223" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1223">
+        <v>16</v>
+      </c>
+      <c r="R1223" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="S1223" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1224" s="1">
+        <v>46225.511631944442</v>
+      </c>
+      <c r="B1224" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1224"/>
+      <c r="F1224">
+        <v>2773312281</v>
+      </c>
+      <c r="G1224" s="2">
+        <v>1784733405355710</v>
+      </c>
+      <c r="H1224" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1224" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1224" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1224" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1224" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1224">
+        <v>19</v>
+      </c>
+      <c r="R1224" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="S1224" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1225" s="1">
+        <v>46225.512453703705</v>
+      </c>
+      <c r="B1225" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1225"/>
+      <c r="F1225">
+        <v>2783266922</v>
+      </c>
+      <c r="G1225" s="2">
+        <v>1784733476357380</v>
+      </c>
+      <c r="H1225" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1225" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1225" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1225" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1225" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1225" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1225">
+        <v>16</v>
+      </c>
+      <c r="R1225" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1225" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1226" s="1">
+        <v>46225.512881944444</v>
+      </c>
+      <c r="B1226" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1226"/>
+      <c r="F1226">
+        <v>2768781018</v>
+      </c>
+      <c r="G1226" s="2">
+        <v>1784733513358210</v>
+      </c>
+      <c r="H1226" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1226" t="s">
+        <v>150</v>
+      </c>
+      <c r="J1226" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1226" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1226" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1226">
+        <v>19</v>
+      </c>
+      <c r="R1226" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="S1226" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1227" s="1">
+        <v>46225.513761574075</v>
+      </c>
+      <c r="B1227" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1227"/>
+      <c r="F1227">
+        <v>2784591317</v>
+      </c>
+      <c r="G1227" s="2">
+        <v>1784733589359850</v>
+      </c>
+      <c r="H1227" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1227" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1227" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1227" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1227" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1227" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1227">
+        <v>16</v>
+      </c>
+      <c r="R1227" s="3">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="S1227" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1228" s="1">
+        <v>46225.514803240738</v>
+      </c>
+      <c r="B1228" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1228"/>
+      <c r="F1228">
+        <v>2784591407</v>
+      </c>
+      <c r="G1228" s="2">
+        <v>1784733679362340</v>
+      </c>
+      <c r="H1228" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1228" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1228" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1228" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1228" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1228" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1228">
+        <v>16</v>
+      </c>
+      <c r="R1228" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="S1228" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1229" s="1">
+        <v>46225.521273148152</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1229"/>
+      <c r="F1229">
+        <v>2760756306</v>
+      </c>
+      <c r="G1229" s="2">
+        <v>1784734238377180</v>
+      </c>
+      <c r="H1229" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1229" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1229" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1229" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1229" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1229">
+        <v>19</v>
+      </c>
+      <c r="R1229" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1229" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1230" s="1">
+        <v>46225.521423611113</v>
+      </c>
+      <c r="B1230" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1230"/>
+      <c r="F1230">
+        <v>2760756319</v>
+      </c>
+      <c r="G1230" s="2">
+        <v>1784734251377520</v>
+      </c>
+      <c r="H1230" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1230" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1230" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1230" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1230" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1230">
+        <v>19</v>
+      </c>
+      <c r="R1230" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1230" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1231" s="1">
+        <v>46225.521793981483</v>
+      </c>
+      <c r="B1231" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1231"/>
+      <c r="F1231">
+        <v>2749396726</v>
+      </c>
+      <c r="G1231" s="2">
+        <v>1784734283378070</v>
+      </c>
+      <c r="H1231" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1231" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1231" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1231" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1231" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1231">
+        <v>19</v>
+      </c>
+      <c r="R1231" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S1231" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1232" s="1">
+        <v>46225.522164351853</v>
+      </c>
+      <c r="B1232" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1232"/>
+      <c r="F1232">
+        <v>2749396757</v>
+      </c>
+      <c r="G1232" s="2">
+        <v>1784734315378610</v>
+      </c>
+      <c r="H1232" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1232" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1232" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1232" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1232" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1232">
+        <v>19</v>
+      </c>
+      <c r="R1232" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="S1232" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1233" s="1">
+        <v>46225.522962962961</v>
+      </c>
+      <c r="B1233" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1233"/>
+      <c r="F1233">
+        <v>2753961127</v>
+      </c>
+      <c r="G1233" s="2">
+        <v>1784734384380290</v>
+      </c>
+      <c r="H1233" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1233" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1233" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1233" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1233" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1233">
+        <v>19</v>
+      </c>
+      <c r="R1233" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1233" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1234" s="1">
+        <v>46225.523148148146</v>
+      </c>
+      <c r="B1234" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1234"/>
+      <c r="F1234">
+        <v>2753961143</v>
+      </c>
+      <c r="G1234" s="2">
+        <v>1784734400380530</v>
+      </c>
+      <c r="H1234" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1234" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1234" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1234" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1234" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1234">
+        <v>19</v>
+      </c>
+      <c r="R1234" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1234" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1235" s="1">
+        <v>46225.523414351854</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1235"/>
+      <c r="F1235">
+        <v>2772744644</v>
+      </c>
+      <c r="G1235" s="2">
+        <v>1784734423381040</v>
+      </c>
+      <c r="H1235" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1235" t="s">
+        <v>155</v>
+      </c>
+      <c r="J1235" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1235" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1235" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1235" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1235">
+        <v>16</v>
+      </c>
+      <c r="R1235" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+      <c r="S1235" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1236" s="1">
+        <v>46225.523761574077</v>
+      </c>
+      <c r="B1236" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1236"/>
+      <c r="F1236">
+        <v>2772744673</v>
+      </c>
+      <c r="G1236" s="2">
+        <v>1784734453381970</v>
+      </c>
+      <c r="H1236" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1236" t="s">
+        <v>155</v>
+      </c>
+      <c r="J1236" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1236" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1236" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1236">
+        <v>19</v>
+      </c>
+      <c r="R1236" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1236" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1237" s="1">
+        <v>46225.524305555555</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1237"/>
+      <c r="F1237">
+        <v>2779005530</v>
+      </c>
+      <c r="G1237" s="2">
+        <v>1784734491382680</v>
+      </c>
+      <c r="H1237" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1237" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1237" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1237" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1237" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1237">
+        <v>17</v>
+      </c>
+      <c r="R1237" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1237" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1238" s="1">
+        <v>46225.524444444447</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1238"/>
+      <c r="F1238">
+        <v>2779005545</v>
+      </c>
+      <c r="G1238" s="2">
+        <v>1784734506383350</v>
+      </c>
+      <c r="H1238" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1238" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1238" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1238" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1238" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1238">
+        <v>17</v>
+      </c>
+      <c r="R1238" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1238" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1239" s="1">
+        <v>46225.524606481478</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1239"/>
+      <c r="F1239">
+        <v>2779005557</v>
+      </c>
+      <c r="G1239" s="2">
+        <v>1784734518383680</v>
+      </c>
+      <c r="H1239" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1239" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1239" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1239" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1239" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1239">
+        <v>17</v>
+      </c>
+      <c r="R1239" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1239" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1240" s="1">
+        <v>46225.524837962963</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1240"/>
+      <c r="F1240">
+        <v>2773053853</v>
+      </c>
+      <c r="G1240" s="2">
+        <v>1784734546384500</v>
+      </c>
+      <c r="H1240" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1240" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1240" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1240" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1240" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1240">
+        <v>19</v>
+      </c>
+      <c r="R1240" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1240" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1241" s="1">
+        <v>46225.524930555555</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1241"/>
+      <c r="F1241">
+        <v>2773053861</v>
+      </c>
+      <c r="G1241" s="2">
+        <v>1784734554384800</v>
+      </c>
+      <c r="H1241" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1241" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1241" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1241" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1241" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1241">
+        <v>19</v>
+      </c>
+      <c r="R1241" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="S1241" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1242" s="1">
+        <v>46225.525300925925</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1242"/>
+      <c r="F1242">
+        <v>2779933030</v>
+      </c>
+      <c r="G1242" s="2">
+        <v>1784734586385350</v>
+      </c>
+      <c r="H1242" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1242" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1242" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1242" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1242" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1242" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1242">
+        <v>16</v>
+      </c>
+      <c r="R1242" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="S1242" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1243" s="1">
+        <v>46225.525763888887</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1243"/>
+      <c r="F1243">
+        <v>2779933070</v>
+      </c>
+      <c r="G1243" s="2">
+        <v>1784734626386290</v>
+      </c>
+      <c r="H1243" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1243" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1243" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1243" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1243" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1243" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1243">
+        <v>16</v>
+      </c>
+      <c r="R1243" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="S1243" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1244" s="1">
+        <v>46225.526203703703</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1244"/>
+      <c r="F1244">
+        <v>2784039443</v>
+      </c>
+      <c r="G1244" s="2">
+        <v>1784734664386920</v>
+      </c>
+      <c r="H1244" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1244" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1244" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1244" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1244" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1244" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1244">
+        <v>16</v>
+      </c>
+      <c r="R1244" s="3">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="S1244" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1245" s="1">
+        <v>46225.52715277778</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1245"/>
+      <c r="F1245">
+        <v>2767795163</v>
+      </c>
+      <c r="G1245" s="2">
+        <v>1784734746388620</v>
+      </c>
+      <c r="H1245" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1245" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1245" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1245" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1245" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1245">
+        <v>19</v>
+      </c>
+      <c r="R1245" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1245" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1246" s="1">
+        <v>46225.527488425927</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1246"/>
+      <c r="F1246">
+        <v>2767795192</v>
+      </c>
+      <c r="G1246" s="2">
+        <v>1784734775389060</v>
+      </c>
+      <c r="H1246" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1246" t="s">
+        <v>162</v>
+      </c>
+      <c r="J1246" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1246" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1246" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1246">
+        <v>19</v>
+      </c>
+      <c r="R1246" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="S1246" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1247" s="1">
+        <v>46225.52815972222</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1247"/>
+      <c r="F1247">
+        <v>2769792966</v>
+      </c>
+      <c r="G1247" s="2">
+        <v>1784734833390370</v>
+      </c>
+      <c r="H1247" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1247" t="s">
+        <v>163</v>
+      </c>
+      <c r="J1247" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1247" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1247" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1247">
+        <v>19</v>
+      </c>
+      <c r="R1247" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1247" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1248" s="1">
+        <v>46225.528298611112</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1248"/>
+      <c r="F1248">
+        <v>2769792979</v>
+      </c>
+      <c r="G1248" s="2">
+        <v>1784734845390590</v>
+      </c>
+      <c r="H1248" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1248" t="s">
+        <v>163</v>
+      </c>
+      <c r="J1248" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1248" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1248" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1248">
+        <v>19</v>
+      </c>
+      <c r="R1248" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1248" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1249" s="1">
+        <v>46225.528425925928</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1249"/>
+      <c r="F1249">
+        <v>2769792989</v>
+      </c>
+      <c r="G1249" s="2">
+        <v>1784734856390910</v>
+      </c>
+      <c r="H1249" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1249" t="s">
+        <v>163</v>
+      </c>
+      <c r="J1249" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1249" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1249" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1249">
+        <v>19</v>
+      </c>
+      <c r="R1249" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1249" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1250" s="1">
+        <v>46225.528703703705</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1250"/>
+      <c r="F1250">
+        <v>2749233624</v>
+      </c>
+      <c r="G1250" s="2">
+        <v>1784734880391630</v>
+      </c>
+      <c r="H1250" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1250" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1250" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1250" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1250" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1250" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1250">
+        <v>16</v>
+      </c>
+      <c r="R1250" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S1250" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1251" s="1">
+        <v>46225.528877314813</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1251"/>
+      <c r="F1251">
+        <v>2749233640</v>
+      </c>
+      <c r="G1251" s="2">
+        <v>1784734895392000</v>
+      </c>
+      <c r="H1251" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1251" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1251" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1251" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1251" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1251" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1251">
+        <v>16</v>
+      </c>
+      <c r="R1251" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="S1251" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1252" s="1">
+        <v>46225.529710648145</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1252"/>
+      <c r="F1252">
+        <v>2777354753</v>
+      </c>
+      <c r="G1252" s="2">
+        <v>1784734967393640</v>
+      </c>
+      <c r="H1252" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1252" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1252" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1252" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1252" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1252">
+        <v>19</v>
+      </c>
+      <c r="R1252" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S1252" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1253" s="1">
+        <v>46225.530057870368</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1253"/>
+      <c r="F1253">
+        <v>2777354783</v>
+      </c>
+      <c r="G1253" s="2">
+        <v>1784734997394220</v>
+      </c>
+      <c r="H1253" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1253" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1253" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1253" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1253" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1253">
+        <v>19</v>
+      </c>
+      <c r="R1253" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S1253" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1254" s="1">
+        <v>46225.530636574076</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1254"/>
+      <c r="F1254">
+        <v>2781890822</v>
+      </c>
+      <c r="G1254" s="2">
+        <v>1784735047395880</v>
+      </c>
+      <c r="H1254" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1254" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1254" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1254" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1254" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1254" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1254">
+        <v>16</v>
+      </c>
+      <c r="R1254" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1254" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1255" s="1">
+        <v>46225.530902777777</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1255"/>
+      <c r="F1255">
+        <v>2781890845</v>
+      </c>
+      <c r="G1255" s="2">
+        <v>1784735070396890</v>
+      </c>
+      <c r="H1255" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1255" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1255" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1255" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1255" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1255" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1255">
+        <v>16</v>
+      </c>
+      <c r="R1255" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1255" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1256" s="1">
+        <v>46225.531307870369</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1256"/>
+      <c r="F1256">
+        <v>2781295056</v>
+      </c>
+      <c r="G1256" s="2">
+        <v>1784735105398230</v>
+      </c>
+      <c r="H1256" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1256" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1256" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1256" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1256" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1256">
+        <v>19</v>
+      </c>
+      <c r="R1256" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1256" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1257" s="1">
+        <v>46225.531458333331</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1257"/>
+      <c r="F1257">
+        <v>2781295069</v>
+      </c>
+      <c r="G1257" s="2">
+        <v>1784735118398720</v>
+      </c>
+      <c r="H1257" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1257" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1257" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1257" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1257" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1257">
+        <v>19</v>
+      </c>
+      <c r="R1257" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1257" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1258" s="1">
+        <v>46225.531863425924</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1258"/>
+      <c r="F1258">
+        <v>2758763691</v>
+      </c>
+      <c r="G1258" s="2">
+        <v>1784735153400100</v>
+      </c>
+      <c r="H1258" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1258" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1258" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1258" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1258" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1258" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1258">
+        <v>16</v>
+      </c>
+      <c r="R1258" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1258" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1259" s="1">
+        <v>46225.532037037039</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1259"/>
+      <c r="F1259">
+        <v>2758763706</v>
+      </c>
+      <c r="G1259" s="2">
+        <v>1784735168400720</v>
+      </c>
+      <c r="H1259" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1259" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1259" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1259" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1259" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1259" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1259">
+        <v>16</v>
+      </c>
+      <c r="R1259" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1259" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1260" s="1">
+        <v>46225.532361111109</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1260"/>
+      <c r="F1260">
+        <v>2751688332</v>
+      </c>
+      <c r="G1260" s="2">
+        <v>1784735196401780</v>
+      </c>
+      <c r="H1260" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1260" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1260" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1260" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1260" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1260">
+        <v>16</v>
+      </c>
+      <c r="R1260" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1260" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1261" s="1">
+        <v>46225.532511574071</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1261"/>
+      <c r="F1261">
+        <v>2751688345</v>
+      </c>
+      <c r="G1261" s="2">
+        <v>1784735209402310</v>
+      </c>
+      <c r="H1261" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1261" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1261" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1261" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1261" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1261">
+        <v>19</v>
+      </c>
+      <c r="R1261" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S1261" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1262" s="1">
+        <v>46225.532881944448</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1262"/>
+      <c r="F1262">
+        <v>2768734985</v>
+      </c>
+      <c r="G1262" s="2">
+        <v>1784735241403550</v>
+      </c>
+      <c r="H1262" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1262" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1262" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1262" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1262" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1262" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1262">
+        <v>16</v>
+      </c>
+      <c r="R1262" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="S1262" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1263" s="1">
+        <v>46225.533067129632</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1263"/>
+      <c r="F1263">
+        <v>2768735001</v>
+      </c>
+      <c r="G1263" s="2">
+        <v>1784735257404150</v>
+      </c>
+      <c r="H1263" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1263" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1263" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1263" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1263" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1263" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1263">
+        <v>16</v>
+      </c>
+      <c r="R1263" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1263" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1264" s="1">
+        <v>46225.533449074072</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1264"/>
+      <c r="F1264">
+        <v>2774797265</v>
+      </c>
+      <c r="G1264" s="2">
+        <v>1784735290405450</v>
+      </c>
+      <c r="H1264" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1264" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1264" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1264" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1264" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1264" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1264">
+        <v>16</v>
+      </c>
+      <c r="R1264" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+      <c r="S1264" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1265" s="1">
+        <v>46225.533831018518</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1265"/>
+      <c r="F1265">
+        <v>2774797298</v>
+      </c>
+      <c r="G1265" s="2">
+        <v>1784735323406350</v>
+      </c>
+      <c r="H1265" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1265" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1265" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1265" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1265" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1265">
+        <v>19</v>
+      </c>
+      <c r="R1265" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="S1265" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1266" s="1">
+        <v>46225.534062500003</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1266"/>
+      <c r="F1266">
+        <v>2780883592</v>
+      </c>
+      <c r="G1266" s="2">
+        <v>1784735343407170</v>
+      </c>
+      <c r="H1266" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1266" t="s">
+        <v>198</v>
+      </c>
+      <c r="J1266" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1266" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1266" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1266">
+        <v>19</v>
+      </c>
+      <c r="R1266" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="S1266" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1267" s="1">
+        <v>46225.534155092595</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1267"/>
+      <c r="F1267">
+        <v>2780883600</v>
+      </c>
+      <c r="G1267" s="2">
+        <v>1784735351407430</v>
+      </c>
+      <c r="H1267" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1267" t="s">
+        <v>198</v>
+      </c>
+      <c r="J1267" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1267" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1267" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1267">
+        <v>19</v>
+      </c>
+      <c r="R1267" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="S1267" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1268" s="1">
+        <v>46225.534837962965</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1268"/>
+      <c r="F1268">
+        <v>2772116096</v>
+      </c>
+      <c r="G1268" s="2">
+        <v>1784735410408990</v>
+      </c>
+      <c r="H1268" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1268" t="s">
+        <v>199</v>
+      </c>
+      <c r="J1268" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1268" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1268" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1268">
+        <v>19</v>
+      </c>
+      <c r="R1268" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S1268" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1269" s="1">
+        <v>46225.535104166665</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1269"/>
+      <c r="F1269">
+        <v>1811374454</v>
+      </c>
+      <c r="G1269" s="2">
+        <v>1784735433409940</v>
+      </c>
+      <c r="H1269" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1269" t="s">
+        <v>200</v>
+      </c>
+      <c r="J1269" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1269" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1269" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1269" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1269">
+        <v>16</v>
+      </c>
+      <c r="R1269" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="S1269" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1270" s="1">
+        <v>46225.536111111112</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1270"/>
+      <c r="F1270">
+        <v>2782615701</v>
+      </c>
+      <c r="G1270" s="2">
+        <v>1784735515412200</v>
+      </c>
+      <c r="H1270" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1270" t="s">
+        <v>201</v>
+      </c>
+      <c r="J1270" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1270" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1270" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1270">
+        <v>17</v>
+      </c>
+      <c r="R1270" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1270" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1271" s="1">
+        <v>46225.536412037036</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1271"/>
+      <c r="F1271">
+        <v>2782615717</v>
+      </c>
+      <c r="G1271" s="2">
+        <v>1784735531412510</v>
+      </c>
+      <c r="H1271" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1271" t="s">
+        <v>201</v>
+      </c>
+      <c r="J1271" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1271" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1271" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1271">
+        <v>17</v>
+      </c>
+      <c r="R1271" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1271" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1272" s="1">
+        <v>46225.53701388889</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1272"/>
+      <c r="F1272">
+        <v>2777725418</v>
+      </c>
+      <c r="G1272" s="2">
+        <v>1784735598413690</v>
+      </c>
+      <c r="H1272" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1272" t="s">
+        <v>202</v>
+      </c>
+      <c r="J1272" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1272" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1272" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1272">
+        <v>19</v>
+      </c>
+      <c r="R1272" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1272" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1273" s="1">
+        <v>46225.537280092591</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1273"/>
+      <c r="F1273">
+        <v>2777725441</v>
+      </c>
+      <c r="G1273" s="2">
+        <v>1784735621413990</v>
+      </c>
+      <c r="H1273" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1273" t="s">
+        <v>202</v>
+      </c>
+      <c r="J1273" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1273" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1273" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1273">
+        <v>19</v>
+      </c>
+      <c r="R1273" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+      <c r="S1273" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1274" s="1">
+        <v>46225.537893518522</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1274"/>
+      <c r="F1274">
+        <v>2773414815</v>
+      </c>
+      <c r="G1274" s="2">
+        <v>1784735674415120</v>
+      </c>
+      <c r="H1274" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1274" t="s">
+        <v>204</v>
+      </c>
+      <c r="J1274" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1274" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1274" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1274">
+        <v>19</v>
+      </c>
+      <c r="R1274" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S1274" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1275" s="1">
+        <v>46225.538217592592</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1275"/>
+      <c r="F1275">
+        <v>2773414843</v>
+      </c>
+      <c r="G1275" s="2">
+        <v>1784735702415640</v>
+      </c>
+      <c r="H1275" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1275" t="s">
+        <v>204</v>
+      </c>
+      <c r="J1275" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1275" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1275" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1275">
+        <v>19</v>
+      </c>
+      <c r="R1275" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="S1275" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1276" s="1">
+        <v>46225.539386574077</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1276"/>
+      <c r="F1276">
+        <v>2754133891</v>
+      </c>
+      <c r="G1276" s="2">
+        <v>1784735743416210</v>
+      </c>
+      <c r="H1276" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1276" t="s">
+        <v>174</v>
+      </c>
+      <c r="J1276" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1276" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1276" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1276">
+        <v>19</v>
+      </c>
+      <c r="R1276" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="S1276" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1277" s="1">
+        <v>46225.539571759262</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1277"/>
+      <c r="F1277">
+        <v>2773185269</v>
+      </c>
+      <c r="G1277" s="2">
+        <v>1784735819417500</v>
+      </c>
+      <c r="H1277" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1277" t="s">
+        <v>177</v>
+      </c>
+      <c r="J1277" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1277" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1277" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1277" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1277">
+        <v>16</v>
+      </c>
+      <c r="R1277" s="3">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="S1277" s="3">
+        <v>9.7222222222222219E-4</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S731" xr:uid="{D24DB4E9-414F-485A-A3F2-E34A8848786F}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
